--- a/人物合集.xlsx
+++ b/人物合集.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\xiaoshuo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{302F90E6-69A1-41F2-9302-E4DBE203EFE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED422C10-28DA-460C-9AFB-48DB28877E6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21820" xr2:uid="{AF08DE20-9936-418E-B994-1A830DDDD9DE}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1294" uniqueCount="856">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1414" uniqueCount="918">
   <si>
     <t>name</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -246,12 +246,6 @@
 姜小满：小师妹
 文梦瑶：初恋
 洛雪茗：恋人</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>姜清竹：师父
-姜小满：小师妹
-莫廉：恋人</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1886,15 +1880,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>甘丽娘：修侣
-凌北风：长子
-凌北照：次子
-凌司辰：外甥
-凌蝶衣：妹妹
-姜清竹：好友</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>凌问天：修侣
 凌北风：长子
 凌北照：次子
@@ -1922,13 +1907,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>凌司辰：好友、仇恨
-姜小满：表妹
-甘丽娘：大姨
-凌北风：表兄</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>凌司辰：追随</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1954,10 +1932,6 @@
   </si>
   <si>
     <t>凌家大公子。拥有【狂影刀】【黑阎罗】【斩太岁】等多重称号的当今仙门最强者，不是正在诛魔，就是在诛魔路上，实力强大，为人沉默寡言。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>风华绝代的凌家二公子，相貌实力皆为仙门佼佼，剑法为自己开创的【邀月剑法】，被称为”仙门最快的剑“</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -2004,22 +1978,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>最年轻的真人，是凌问天的小师弟。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>凌问天：师兄</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>凌司辰的母亲，因背弃婚约叛逃于十八年前被逐出宗门不许回归。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>凌司辰：儿子
-归尘：伴侣
-凌问天：兄长
-甘丽娘：师妹</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -2105,10 +2068,6 @@
   </si>
   <si>
     <t>柳夫人</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>罗云禾</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -2536,30 +2495,9 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>文伯良：兄长
-文梦语：女儿
-班淑：修侣
-柳夫人：修侣</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>文伯良：父亲
-文志成：弟弟
-文梦语：堂妹</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>文伯良：父亲
 文梦瑶：长姊
 文梦语：堂妹</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>文梦瑶：修侣</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>文梦语：女儿</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -2856,10 +2794,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>菩提：自己</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>七百年前的铜虎尊者。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2917,15 +2851,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>姜小满（魔君）：自己
-凌司辰：恋人
-羽霜：好友
-文梦语：复杂
-莫廉：大师兄
-洛雪茗：师姐</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>西渊的君主，火脉之主，豪爽好战、力大无穷。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2997,6 +2922,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>500+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>南渊白鸾，四鸾出生顺序第三，十杰将之五。主君不在时，南渊出征军的主帅。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -3024,6 +2953,9 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>飓衍：主君</t>
+  </si>
+  <si>
     <t>飓衍：信赖/主君
 灾凤：信赖/姐姐
 羽霜：信赖/姐姐
@@ -3050,19 +2982,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>凌啸云：飞升前</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>裴卿卿：飞升前</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>金翎神女：飞升后</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>丹炉掌者，一般不出门。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -3135,14 +3055,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>阳骞：自己
-云海战神：下属
-金翎神女：下属
-乾罗武圣：下属
-砺风战神：下属</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>掌管术艺技法之主神。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -3157,13 +3069,6 @@
   </si>
   <si>
     <t>子桑怜：自己</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>姬若羽：自己
-柏洺仙君：下属
-梅鹤仙君：下属
-「兵器」：傀儡</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -3227,6 +3132,404 @@
   </si>
   <si>
     <t>焚冲君门中食客。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>凌司辰：儿子
+归尘：伴侣
+凌问天：兄长
+甘丽娘：师妹
+凌正晟：父亲</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>凌问天：儿子
+凌蝶衣：女儿</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>甘丽娘：修侣
+凌北风：长子
+凌北照：次子
+凌司辰：外甥
+凌蝶衣：妹妹
+姜清竹：好友
+凌正晟：父亲</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>蓬莱三战神之一，已故。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>凌北风：飞升前
+凌司辰：敌对
+羽霜：偏执</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>蓬莱新飞升的战神，为最强法相“白猿”承载者。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>蓬莱三战神之一，人称【火云脚】，法相“黑虎”承载者。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>蓬莱三战神之一，使一柄神剑【青罡】，法相“金羊”承载者。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>擅长机关秘术的神仙。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>蓬莱文神，相貌出众但油嘴滑舌。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>蓬莱武神。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>云海战神的仙侍。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>焚冲仙尊：上司</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>雉羽仙尊：上司
+云海战神：好友</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>凌啸云：飞升前
+凌北风：徒弟
+天元仙尊：上司
+金翎神女：同僚
+砺风战神：同僚
+柏洺仙君：好友
+庚丑：仙侍
+壬午：仙侍</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>裴卿卿：飞升前
+天元仙尊：上司
+云海战神：同僚
+砺风战神：同僚
+凌蝶衣：徒弟
+铃兰：仙侍</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>天元仙尊：上司
+云海战神：同僚
+金翎神女：同僚</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>蓬莱文神。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>姬若羽：自己
+柏洺仙君：下属
+梅孺仙君：下属
+梅鹤仙君：下属
+「兵器」：傀儡</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>雉羽仙尊：上司</t>
+  </si>
+  <si>
+    <t>阳骞：自己
+云海战神：下属
+金翎神女：下属
+乾罗武圣：下属
+砺风战神：下属
+明瞳仙君：下属</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>天元仙尊：上司</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>云海战神：主仙</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>金翎神女的仙侍。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>金翎神女：主仙
+图娜：女儿</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>飓衍：主君
+灰枫：同僚</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>飓衍：主君
+羌笛：同僚</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>文梦语：好友</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>无</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>传说中不为人知的“第四法相”承载者。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>风华绝代的凌家二公子，使用自己开创的【邀月剑法】，被称为“仙门最快的剑”。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>岳山十二真人之一。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>岳山十二真人之一，资历最老。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>岳山十二真人之一，最年轻的真人，是凌问天的小师弟。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>拳修，司徒燕的师弟。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>力大无穷，使一柄红莲枪。为为金翎神女之后第二位玄阳女修，有望成为下一任铁豹尊者。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>铁豹尊者：师尊
+银狮尊者：尊伯
+铜虎尊者：尊叔
+乾允：师弟
+洛雪茗：好友
+姜小满：好友</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>姜小满（魔君）：自己
+凌司辰：恋人
+姜清竹：父亲
+姜榕：大姑
+莫廉：大师兄
+洛雪茗：师姐
+冯梨儿：好友/师姐
+余萝：师姐
+齐茵：师姐
+羽霜：好友
+文梦语：复杂
+司徒燕：好友
+荆藜：母亲（已故）
+荆芸：小姨
+裘万里：小姨夫</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>姜清竹：师父
+姜小满：小师妹
+莫廉：恋人
+余萝：好友
+司徒燕：好友</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>文伯良：父亲
+文志成：弟弟
+文梦语：堂妹
+莫廉：初恋
+罗云禾：修侣</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>陨星：退宗前
+文梦瑶：修侣</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>罗允禾：退宗后</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>罗允禾</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>文梦语：小姐</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>文伯远：修侣（前）
+文梦语：女儿</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>文伯良：兄长
+文梦语：女儿
+班淑：修侣（前）
+柳夫人：修侣</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>文伯远：修侣</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>玄阳三尊者之首。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>玄阳三尊者之一。</t>
+  </si>
+  <si>
+    <t>玄阳三尊者之一。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>铁豹尊者：师弟
+铜虎尊者：师弟</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>银狮尊者：师兄
+铜虎尊者：师弟
+司徒燕：徒弟
+乾允：徒弟</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>银狮尊者：师兄
+铁豹尊者：师兄</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>东南渔村</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>铁豹尊者：师尊
+司徒燕：师姐</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>凌司辰：好友/仇恨
+姜小满：表妹
+甘丽娘：大姨
+凌北风：表兄</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>苍龙七星之首。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>苍龙七星之一，丹炉掌者，一般不出门。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>苍龙七星之一。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>玉清门修士。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>角宿：师尊
+心宿：师尊</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>亢宿：师尊</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>菩提：自己
+丰星：徒弟
+永星：徒弟</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>拜火教少城主。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>热情似火的大漠姑娘。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>拜火教老城主。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>千香楼的医术师。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>千香楼妓女。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>库尔台：未婚夫
+铃兰：母亲</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>库尔台：儿子</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>胡四娘：依靠</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>铃兰：结义姐妹
+阿贺：照顾</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>彝城包子铺的老板娘，似乎与大漠拜火教有瓜葛。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>芦城边缘的算账人。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>大漠</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>大荒原的神秘来客。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>库尔台：好友</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>图娜：未婚妻
+老城主：父亲
+法鲁克：好友</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3634,16 +3937,16 @@
         <v>24</v>
       </c>
       <c r="I1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="J1" t="s">
         <v>5</v>
       </c>
       <c r="K1" t="s">
-        <v>509</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" ht="84" x14ac:dyDescent="0.3">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="210" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>49</v>
       </c>
@@ -3657,7 +3960,7 @@
         <v>21</v>
       </c>
       <c r="E2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F2">
         <v>17</v>
@@ -3672,7 +3975,7 @@
         <v>42</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>793</v>
+        <v>877</v>
       </c>
       <c r="K2">
         <v>1</v>
@@ -3680,7 +3983,7 @@
     </row>
     <row r="3" spans="1:11" ht="56" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B3" t="s">
         <v>7</v>
@@ -3692,7 +3995,7 @@
         <v>23</v>
       </c>
       <c r="E3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F3">
         <v>29</v>
@@ -3713,9 +4016,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="42" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" ht="70" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B4" t="s">
         <v>8</v>
@@ -3727,7 +4030,7 @@
         <v>21</v>
       </c>
       <c r="E4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F4">
         <v>24</v>
@@ -3742,7 +4045,7 @@
         <v>47</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>51</v>
+        <v>878</v>
       </c>
       <c r="K4">
         <v>1</v>
@@ -3750,7 +4053,7 @@
     </row>
     <row r="5" spans="1:11" ht="56" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B5" t="s">
         <v>9</v>
@@ -3762,7 +4065,7 @@
         <v>23</v>
       </c>
       <c r="E5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F5">
         <v>44</v>
@@ -3777,7 +4080,7 @@
         <v>46</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K5">
         <v>1</v>
@@ -3785,7 +4088,7 @@
     </row>
     <row r="6" spans="1:11" ht="56" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B6" t="s">
         <v>10</v>
@@ -3797,7 +4100,7 @@
         <v>21</v>
       </c>
       <c r="E6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F6">
         <v>45</v>
@@ -3812,7 +4115,7 @@
         <v>44</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="K6">
         <v>1</v>
@@ -3820,7 +4123,7 @@
     </row>
     <row r="7" spans="1:11" ht="56" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B7" t="s">
         <v>11</v>
@@ -3832,7 +4135,7 @@
         <v>21</v>
       </c>
       <c r="E7" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F7">
         <v>25</v>
@@ -3847,7 +4150,7 @@
         <v>41</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="K7">
         <v>1</v>
@@ -3855,7 +4158,7 @@
     </row>
     <row r="8" spans="1:11" ht="56" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B8" t="s">
         <v>12</v>
@@ -3867,7 +4170,7 @@
         <v>21</v>
       </c>
       <c r="E8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F8">
         <v>24</v>
@@ -3882,7 +4185,7 @@
         <v>46</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="K8">
         <v>1</v>
@@ -3890,7 +4193,7 @@
     </row>
     <row r="9" spans="1:11" ht="42" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B9" t="s">
         <v>13</v>
@@ -3902,7 +4205,7 @@
         <v>21</v>
       </c>
       <c r="E9" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F9">
         <v>18</v>
@@ -3917,7 +4220,7 @@
         <v>42</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="K9">
         <v>1</v>
@@ -3925,7 +4228,7 @@
     </row>
     <row r="10" spans="1:11" ht="42" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B10" t="s">
         <v>14</v>
@@ -3937,7 +4240,7 @@
         <v>23</v>
       </c>
       <c r="E10" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F10">
         <v>20</v>
@@ -3952,7 +4255,7 @@
         <v>41</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K10">
         <v>1</v>
@@ -3960,7 +4263,7 @@
     </row>
     <row r="11" spans="1:11" ht="42" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B11" t="s">
         <v>15</v>
@@ -3972,7 +4275,7 @@
         <v>23</v>
       </c>
       <c r="E11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F11">
         <v>24</v>
@@ -3987,7 +4290,7 @@
         <v>43</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="K11">
         <v>1</v>
@@ -3995,7 +4298,7 @@
     </row>
     <row r="12" spans="1:11" ht="42" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B12" t="s">
         <v>16</v>
@@ -4007,7 +4310,7 @@
         <v>23</v>
       </c>
       <c r="E12" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F12">
         <v>23</v>
@@ -4022,7 +4325,7 @@
         <v>45</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="K12">
         <v>1</v>
@@ -4030,7 +4333,7 @@
     </row>
     <row r="13" spans="1:11" ht="42" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B13" t="s">
         <v>17</v>
@@ -4042,7 +4345,7 @@
         <v>21</v>
       </c>
       <c r="E13" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F13" t="s">
         <v>27</v>
@@ -4057,7 +4360,7 @@
         <v>46</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="K13">
         <v>1</v>
@@ -4065,7 +4368,7 @@
     </row>
     <row r="14" spans="1:11" ht="42" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B14" t="s">
         <v>18</v>
@@ -4077,7 +4380,7 @@
         <v>21</v>
       </c>
       <c r="E14" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F14">
         <v>38</v>
@@ -4092,7 +4395,7 @@
         <v>43</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="K14">
         <v>1</v>
@@ -4100,7 +4403,7 @@
     </row>
     <row r="15" spans="1:11" ht="42" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B15" t="s">
         <v>19</v>
@@ -4112,7 +4415,7 @@
         <v>23</v>
       </c>
       <c r="E15" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F15">
         <v>37</v>
@@ -4127,7 +4430,7 @@
         <v>46</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K15">
         <v>1</v>
@@ -4135,7 +4438,7 @@
     </row>
     <row r="16" spans="1:11" ht="42" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B16" t="s">
         <v>26</v>
@@ -4147,7 +4450,7 @@
         <v>23</v>
       </c>
       <c r="E16" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F16" t="s">
         <v>29</v>
@@ -4162,7 +4465,7 @@
         <v>48</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="K16">
         <v>1</v>
@@ -4170,19 +4473,19 @@
     </row>
     <row r="17" spans="1:11" ht="84" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B17" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C17" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="D17" t="s">
         <v>23</v>
       </c>
       <c r="E17" t="s">
-        <v>571</v>
+        <v>870</v>
       </c>
       <c r="F17">
         <v>19</v>
@@ -4191,13 +4494,13 @@
         <v>184</v>
       </c>
       <c r="H17" t="s">
+        <v>542</v>
+      </c>
+      <c r="I17" t="s">
         <v>543</v>
       </c>
-      <c r="I17" t="s">
-        <v>544</v>
-      </c>
       <c r="J17" s="1" t="s">
-        <v>767</v>
+        <v>756</v>
       </c>
       <c r="K17">
         <v>1</v>
@@ -4205,19 +4508,19 @@
     </row>
     <row r="18" spans="1:11" ht="84" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B18" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="C18" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="D18" t="s">
         <v>23</v>
       </c>
       <c r="E18" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="F18">
         <v>26</v>
@@ -4226,33 +4529,33 @@
         <v>188</v>
       </c>
       <c r="H18" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="I18" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="K18">
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:11" ht="84" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:11" ht="98" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B19" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C19" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="D19" t="s">
         <v>23</v>
       </c>
       <c r="E19" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="F19">
         <v>60</v>
@@ -4261,13 +4564,13 @@
         <v>185</v>
       </c>
       <c r="H19" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="I19" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>558</v>
+        <v>842</v>
       </c>
       <c r="K19">
         <v>1</v>
@@ -4275,19 +4578,19 @@
     </row>
     <row r="20" spans="1:11" ht="56" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B20" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="C20" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="D20" t="s">
         <v>21</v>
       </c>
       <c r="E20" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="F20">
         <v>43</v>
@@ -4296,13 +4599,13 @@
         <v>175</v>
       </c>
       <c r="H20" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="I20" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="K20">
         <v>1</v>
@@ -4310,19 +4613,19 @@
     </row>
     <row r="21" spans="1:11" ht="56" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B21" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="C21" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="D21" t="s">
         <v>23</v>
       </c>
       <c r="E21" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="F21">
         <v>7</v>
@@ -4331,13 +4634,13 @@
         <v>130</v>
       </c>
       <c r="H21" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="I21" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="K21">
         <v>1</v>
@@ -4345,19 +4648,19 @@
     </row>
     <row r="22" spans="1:11" ht="70" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B22" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C22" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="D22" t="s">
         <v>23</v>
       </c>
       <c r="E22" t="s">
-        <v>572</v>
+        <v>568</v>
       </c>
       <c r="F22">
         <v>22</v>
@@ -4369,10 +4672,10 @@
         <v>31</v>
       </c>
       <c r="I22" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="K22">
         <v>1</v>
@@ -4380,19 +4683,19 @@
     </row>
     <row r="23" spans="1:11" ht="28" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B23" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C23" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="D23" t="s">
         <v>23</v>
       </c>
       <c r="E23" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="F23">
         <v>21</v>
@@ -4404,10 +4707,10 @@
         <v>33</v>
       </c>
       <c r="I23" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="K23">
         <v>1</v>
@@ -4415,19 +4718,19 @@
     </row>
     <row r="24" spans="1:11" ht="56" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B24" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="C24" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="D24" t="s">
         <v>23</v>
       </c>
       <c r="E24" t="s">
-        <v>574</v>
+        <v>570</v>
       </c>
       <c r="F24">
         <v>17</v>
@@ -4439,10 +4742,10 @@
         <v>34</v>
       </c>
       <c r="I24" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>563</v>
+        <v>895</v>
       </c>
       <c r="K24">
         <v>1</v>
@@ -4450,19 +4753,19 @@
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B25" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C25" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="D25" t="s">
         <v>23</v>
       </c>
       <c r="E25" t="s">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="F25">
         <v>15</v>
@@ -4474,10 +4777,10 @@
         <v>35</v>
       </c>
       <c r="I25" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="K25">
         <v>1</v>
@@ -4485,19 +4788,19 @@
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B26" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="C26" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="D26" t="s">
         <v>23</v>
       </c>
       <c r="E26" t="s">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="F26">
         <v>20</v>
@@ -4509,10 +4812,10 @@
         <v>33</v>
       </c>
       <c r="I26" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="K26">
         <v>1</v>
@@ -4520,19 +4823,19 @@
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B27" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="C27" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="D27" t="s">
         <v>23</v>
       </c>
       <c r="E27" t="s">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="F27">
         <v>19</v>
@@ -4544,10 +4847,10 @@
         <v>34</v>
       </c>
       <c r="I27" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="K27">
         <v>1</v>
@@ -4555,19 +4858,19 @@
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B28" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="C28" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="D28" t="s">
         <v>21</v>
       </c>
       <c r="E28" t="s">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="F28">
         <v>17</v>
@@ -4579,10 +4882,10 @@
         <v>31</v>
       </c>
       <c r="I28" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="K28">
         <v>1</v>
@@ -4590,19 +4893,19 @@
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B29" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="C29" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="D29" t="s">
         <v>21</v>
       </c>
       <c r="E29" t="s">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="F29">
         <v>22</v>
@@ -4614,7 +4917,7 @@
         <v>34</v>
       </c>
       <c r="I29" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="K29">
         <v>1</v>
@@ -4622,34 +4925,34 @@
     </row>
     <row r="30" spans="1:11" ht="42" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B30" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C30" t="s">
+        <v>539</v>
+      </c>
+      <c r="D30" t="s">
+        <v>23</v>
+      </c>
+      <c r="E30" t="s">
+        <v>573</v>
+      </c>
+      <c r="F30" t="s">
         <v>540</v>
-      </c>
-      <c r="D30" t="s">
-        <v>23</v>
-      </c>
-      <c r="E30" t="s">
-        <v>577</v>
-      </c>
-      <c r="F30" t="s">
-        <v>541</v>
       </c>
       <c r="G30">
         <v>150</v>
       </c>
       <c r="H30" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="I30" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="K30">
         <v>1</v>
@@ -4657,19 +4960,19 @@
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B31" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="C31" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="D31" t="s">
         <v>23</v>
       </c>
       <c r="E31" t="s">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="F31">
         <v>58</v>
@@ -4681,10 +4984,10 @@
         <v>34</v>
       </c>
       <c r="I31" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="J31" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="K31">
         <v>1</v>
@@ -4692,16 +4995,19 @@
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="B32" t="s">
         <v>522</v>
       </c>
-      <c r="B32" t="s">
-        <v>523</v>
-      </c>
       <c r="C32" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="D32" t="s">
         <v>23</v>
+      </c>
+      <c r="E32" t="s">
+        <v>872</v>
       </c>
       <c r="F32">
         <v>62</v>
@@ -4710,13 +5016,13 @@
         <v>180</v>
       </c>
       <c r="H32" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="I32" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="J32" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="K32">
         <v>1</v>
@@ -4724,16 +5030,19 @@
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B33" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C33" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="D33" t="s">
         <v>23</v>
+      </c>
+      <c r="E33" t="s">
+        <v>871</v>
       </c>
       <c r="F33">
         <v>55</v>
@@ -4745,10 +5054,10 @@
         <v>30</v>
       </c>
       <c r="I33" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="J33" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="K33">
         <v>1</v>
@@ -4756,17 +5065,20 @@
     </row>
     <row r="34" spans="1:11" ht="28" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B34" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="C34" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="D34" t="s">
         <v>21</v>
       </c>
+      <c r="E34" t="s">
+        <v>871</v>
+      </c>
       <c r="F34">
         <v>52</v>
       </c>
@@ -4777,10 +5089,10 @@
         <v>37</v>
       </c>
       <c r="I34" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>581</v>
+        <v>577</v>
       </c>
       <c r="K34">
         <v>1</v>
@@ -4788,16 +5100,19 @@
     </row>
     <row r="35" spans="1:11" ht="28" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B35" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="C35" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="D35" t="s">
         <v>23</v>
+      </c>
+      <c r="E35" t="s">
+        <v>871</v>
       </c>
       <c r="F35">
         <v>55</v>
@@ -4809,10 +5124,10 @@
         <v>37</v>
       </c>
       <c r="I35" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="J35" s="1" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="K35">
         <v>1</v>
@@ -4820,19 +5135,19 @@
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B36" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="C36" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="D36" t="s">
         <v>23</v>
       </c>
       <c r="E36" t="s">
-        <v>582</v>
+        <v>873</v>
       </c>
       <c r="F36">
         <v>45</v>
@@ -4844,10 +5159,10 @@
         <v>34</v>
       </c>
       <c r="I36" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="J36" t="s">
-        <v>583</v>
+        <v>578</v>
       </c>
       <c r="K36">
         <v>1</v>
@@ -4855,17 +5170,20 @@
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B37" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C37" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="D37" t="s">
         <v>21</v>
       </c>
+      <c r="E37" t="s">
+        <v>871</v>
+      </c>
       <c r="F37">
         <v>57</v>
       </c>
@@ -4876,10 +5194,10 @@
         <v>34</v>
       </c>
       <c r="I37" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="J37" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="K37">
         <v>1</v>
@@ -4887,16 +5205,19 @@
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B38" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C38" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="D38" t="s">
         <v>23</v>
+      </c>
+      <c r="E38" t="s">
+        <v>871</v>
       </c>
       <c r="F38">
         <v>56</v>
@@ -4908,10 +5229,10 @@
         <v>39</v>
       </c>
       <c r="I38" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="J38" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="K38">
         <v>1</v>
@@ -4919,16 +5240,19 @@
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B39" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="C39" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="D39" t="s">
         <v>23</v>
+      </c>
+      <c r="E39" t="s">
+        <v>871</v>
       </c>
       <c r="F39">
         <v>50</v>
@@ -4937,80 +5261,83 @@
         <v>169</v>
       </c>
       <c r="H39" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="I39" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="J39" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="K39">
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:11" ht="56" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:11" ht="70" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B40" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="C40" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="D40" t="s">
         <v>21</v>
       </c>
       <c r="E40" t="s">
-        <v>584</v>
+        <v>579</v>
       </c>
       <c r="F40" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="G40">
         <v>168</v>
       </c>
       <c r="H40" t="s">
+        <v>542</v>
+      </c>
+      <c r="I40" t="s">
         <v>543</v>
       </c>
-      <c r="I40" t="s">
-        <v>544</v>
-      </c>
       <c r="J40" s="1" t="s">
-        <v>585</v>
+        <v>840</v>
       </c>
       <c r="K40">
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:11" ht="28" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B41" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="C41" t="s">
+        <v>539</v>
+      </c>
+      <c r="D41" t="s">
+        <v>23</v>
+      </c>
+      <c r="E41" t="s">
+        <v>580</v>
+      </c>
+      <c r="F41" t="s">
+        <v>581</v>
+      </c>
+      <c r="G41" t="s">
         <v>540</v>
       </c>
-      <c r="D41" t="s">
-        <v>23</v>
-      </c>
-      <c r="E41" t="s">
-        <v>586</v>
-      </c>
-      <c r="F41" t="s">
-        <v>587</v>
-      </c>
-      <c r="G41" t="s">
-        <v>541</v>
-      </c>
       <c r="H41" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="I41" t="s">
-        <v>541</v>
+        <v>540</v>
+      </c>
+      <c r="J41" s="1" t="s">
+        <v>841</v>
       </c>
       <c r="K41">
         <v>1</v>
@@ -5018,34 +5345,34 @@
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B42" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="C42" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="D42" t="s">
         <v>21</v>
       </c>
       <c r="E42" t="s">
-        <v>588</v>
+        <v>582</v>
       </c>
       <c r="F42" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="G42" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="H42" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="I42" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="J42" t="s">
-        <v>591</v>
+        <v>585</v>
       </c>
       <c r="K42">
         <v>1</v>
@@ -5053,34 +5380,34 @@
     </row>
     <row r="43" spans="1:11" ht="56" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B43" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="C43" t="s">
+        <v>539</v>
+      </c>
+      <c r="D43" t="s">
+        <v>23</v>
+      </c>
+      <c r="E43" t="s">
+        <v>583</v>
+      </c>
+      <c r="F43" t="s">
         <v>540</v>
       </c>
-      <c r="D43" t="s">
-        <v>23</v>
-      </c>
-      <c r="E43" t="s">
-        <v>589</v>
-      </c>
-      <c r="F43" t="s">
-        <v>541</v>
-      </c>
-      <c r="G43" t="s">
-        <v>541</v>
+      <c r="G43">
+        <v>187</v>
       </c>
       <c r="H43" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="I43" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="J43" s="1" t="s">
-        <v>592</v>
+        <v>586</v>
       </c>
       <c r="K43">
         <v>1</v>
@@ -5088,34 +5415,34 @@
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B44" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C44" t="s">
+        <v>539</v>
+      </c>
+      <c r="D44" t="s">
+        <v>23</v>
+      </c>
+      <c r="E44" t="s">
+        <v>584</v>
+      </c>
+      <c r="F44" t="s">
         <v>540</v>
       </c>
-      <c r="D44" t="s">
-        <v>23</v>
-      </c>
-      <c r="E44" t="s">
-        <v>590</v>
-      </c>
-      <c r="F44" t="s">
-        <v>541</v>
-      </c>
       <c r="G44" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="H44" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="I44" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="J44" t="s">
-        <v>593</v>
+        <v>587</v>
       </c>
       <c r="K44">
         <v>1</v>
@@ -5123,25 +5450,25 @@
     </row>
     <row r="45" spans="1:11" ht="28" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B45" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="C45" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="D45" t="s">
         <v>21</v>
       </c>
       <c r="E45" t="s">
-        <v>595</v>
+        <v>589</v>
       </c>
       <c r="F45" t="s">
         <v>28</v>
       </c>
       <c r="G45" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="H45" t="s">
         <v>30</v>
@@ -5150,7 +5477,7 @@
         <v>40</v>
       </c>
       <c r="J45" s="1" t="s">
-        <v>594</v>
+        <v>588</v>
       </c>
       <c r="K45">
         <v>1</v>
@@ -5158,34 +5485,34 @@
     </row>
     <row r="46" spans="1:11" ht="28" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B46" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="C46" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="D46" t="s">
         <v>21</v>
       </c>
       <c r="E46" t="s">
-        <v>596</v>
+        <v>590</v>
       </c>
       <c r="F46" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="G46" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="H46" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="I46" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="J46" s="1" t="s">
-        <v>598</v>
+        <v>592</v>
       </c>
       <c r="K46">
         <v>1</v>
@@ -5193,31 +5520,31 @@
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
+        <v>537</v>
+      </c>
+      <c r="B47" t="s">
         <v>538</v>
       </c>
-      <c r="B47" t="s">
+      <c r="C47" t="s">
         <v>539</v>
       </c>
-      <c r="C47" t="s">
+      <c r="D47" t="s">
+        <v>23</v>
+      </c>
+      <c r="E47" t="s">
+        <v>591</v>
+      </c>
+      <c r="F47" t="s">
         <v>540</v>
       </c>
-      <c r="D47" t="s">
-        <v>23</v>
-      </c>
-      <c r="E47" t="s">
-        <v>597</v>
-      </c>
-      <c r="F47" t="s">
-        <v>541</v>
-      </c>
       <c r="G47" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="H47" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="I47" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="K47">
         <v>1</v>
@@ -5225,19 +5552,19 @@
     </row>
     <row r="48" spans="1:11" ht="98" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B48" t="s">
-        <v>599</v>
+        <v>593</v>
       </c>
       <c r="C48" t="s">
-        <v>706</v>
+        <v>699</v>
       </c>
       <c r="D48" t="s">
         <v>21</v>
       </c>
       <c r="E48" t="s">
-        <v>716</v>
+        <v>705</v>
       </c>
       <c r="F48">
         <v>19</v>
@@ -5246,10 +5573,10 @@
         <v>160</v>
       </c>
       <c r="H48" t="s">
-        <v>707</v>
+        <v>700</v>
       </c>
       <c r="J48" s="1" t="s">
-        <v>708</v>
+        <v>701</v>
       </c>
       <c r="K48">
         <v>1</v>
@@ -5257,19 +5584,19 @@
     </row>
     <row r="49" spans="1:11" ht="42" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B49" t="s">
-        <v>600</v>
+        <v>594</v>
       </c>
       <c r="C49" t="s">
-        <v>706</v>
+        <v>699</v>
       </c>
       <c r="D49" t="s">
         <v>23</v>
       </c>
       <c r="E49" t="s">
-        <v>720</v>
+        <v>709</v>
       </c>
       <c r="F49">
         <v>44</v>
@@ -5278,10 +5605,10 @@
         <v>185</v>
       </c>
       <c r="H49" t="s">
-        <v>707</v>
+        <v>700</v>
       </c>
       <c r="J49" s="1" t="s">
-        <v>710</v>
+        <v>703</v>
       </c>
       <c r="K49">
         <v>1</v>
@@ -5289,19 +5616,19 @@
     </row>
     <row r="50" spans="1:11" ht="56" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B50" t="s">
-        <v>601</v>
+        <v>595</v>
       </c>
       <c r="C50" t="s">
-        <v>706</v>
+        <v>699</v>
       </c>
       <c r="D50" t="s">
         <v>23</v>
       </c>
       <c r="E50" t="s">
-        <v>721</v>
+        <v>710</v>
       </c>
       <c r="F50">
         <v>42</v>
@@ -5310,30 +5637,30 @@
         <v>186</v>
       </c>
       <c r="H50" t="s">
-        <v>707</v>
+        <v>700</v>
       </c>
       <c r="J50" s="1" t="s">
-        <v>711</v>
+        <v>885</v>
       </c>
       <c r="K50">
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:11" ht="42" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:11" ht="70" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B51" t="s">
-        <v>602</v>
+        <v>596</v>
       </c>
       <c r="C51" t="s">
-        <v>706</v>
+        <v>699</v>
       </c>
       <c r="D51" t="s">
         <v>21</v>
       </c>
       <c r="E51" t="s">
-        <v>722</v>
+        <v>711</v>
       </c>
       <c r="F51">
         <v>26</v>
@@ -5342,10 +5669,10 @@
         <v>172</v>
       </c>
       <c r="H51" t="s">
-        <v>707</v>
+        <v>700</v>
       </c>
       <c r="J51" s="1" t="s">
-        <v>712</v>
+        <v>879</v>
       </c>
       <c r="K51">
         <v>1</v>
@@ -5353,19 +5680,19 @@
     </row>
     <row r="52" spans="1:11" ht="42" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B52" t="s">
-        <v>603</v>
+        <v>597</v>
       </c>
       <c r="C52" t="s">
-        <v>706</v>
+        <v>699</v>
       </c>
       <c r="D52" t="s">
         <v>23</v>
       </c>
       <c r="E52" t="s">
-        <v>723</v>
+        <v>712</v>
       </c>
       <c r="F52">
         <v>21</v>
@@ -5374,33 +5701,33 @@
         <v>179</v>
       </c>
       <c r="H52" t="s">
-        <v>707</v>
+        <v>700</v>
       </c>
       <c r="J52" s="1" t="s">
-        <v>713</v>
+        <v>704</v>
       </c>
       <c r="K52">
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:11" ht="28" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B53" t="s">
-        <v>604</v>
+        <v>598</v>
       </c>
       <c r="C53" t="s">
-        <v>706</v>
+        <v>699</v>
       </c>
       <c r="D53" t="s">
         <v>21</v>
       </c>
       <c r="E53" t="s">
-        <v>724</v>
+        <v>713</v>
       </c>
       <c r="F53" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="G53">
         <v>158</v>
@@ -5409,7 +5736,7 @@
         <v>34</v>
       </c>
       <c r="J53" s="1" t="s">
-        <v>715</v>
+        <v>884</v>
       </c>
       <c r="K53">
         <v>1</v>
@@ -5417,19 +5744,19 @@
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B54" t="s">
-        <v>605</v>
+        <v>599</v>
       </c>
       <c r="C54" t="s">
-        <v>706</v>
+        <v>699</v>
       </c>
       <c r="D54" t="s">
         <v>21</v>
       </c>
       <c r="E54" t="s">
-        <v>725</v>
+        <v>714</v>
       </c>
       <c r="F54">
         <v>29</v>
@@ -5440,25 +5767,28 @@
       <c r="H54" t="s">
         <v>37</v>
       </c>
+      <c r="J54" s="1" t="s">
+        <v>886</v>
+      </c>
       <c r="K54">
         <v>1</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B55" t="s">
-        <v>717</v>
+        <v>706</v>
       </c>
       <c r="C55" t="s">
-        <v>706</v>
+        <v>699</v>
       </c>
       <c r="D55" t="s">
         <v>21</v>
       </c>
       <c r="E55" t="s">
-        <v>719</v>
+        <v>708</v>
       </c>
       <c r="F55">
         <v>16</v>
@@ -5467,27 +5797,30 @@
         <v>152</v>
       </c>
       <c r="H55" t="s">
-        <v>718</v>
+        <v>707</v>
+      </c>
+      <c r="J55" s="1" t="s">
+        <v>883</v>
       </c>
       <c r="K55">
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:11" ht="28" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B56" t="s">
-        <v>606</v>
+        <v>882</v>
       </c>
       <c r="C56" t="s">
-        <v>726</v>
+        <v>715</v>
       </c>
       <c r="D56" t="s">
         <v>23</v>
       </c>
       <c r="E56" t="s">
-        <v>728</v>
+        <v>717</v>
       </c>
       <c r="F56">
         <v>28</v>
@@ -5499,1441 +5832,1765 @@
         <v>31</v>
       </c>
       <c r="J56" s="1" t="s">
-        <v>714</v>
+        <v>880</v>
       </c>
       <c r="K56">
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:11" ht="28" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="B57" t="s">
+        <v>600</v>
+      </c>
+      <c r="C57" t="s">
+        <v>718</v>
+      </c>
+      <c r="D57" t="s">
+        <v>23</v>
+      </c>
+      <c r="E57" t="s">
+        <v>887</v>
+      </c>
+      <c r="F57">
+        <v>73</v>
+      </c>
+      <c r="G57">
+        <v>186</v>
+      </c>
+      <c r="H57" t="s">
+        <v>34</v>
+      </c>
+      <c r="J57" s="1" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" ht="56" x14ac:dyDescent="0.3">
+      <c r="A58" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="B57" t="s">
-        <v>607</v>
-      </c>
-      <c r="C57" t="s">
-        <v>729</v>
-      </c>
-      <c r="D57" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A58" s="2" t="s">
+      <c r="B58" t="s">
+        <v>601</v>
+      </c>
+      <c r="C58" t="s">
+        <v>718</v>
+      </c>
+      <c r="D58" t="s">
+        <v>23</v>
+      </c>
+      <c r="E58" t="s">
+        <v>889</v>
+      </c>
+      <c r="F58">
+        <v>65</v>
+      </c>
+      <c r="G58">
+        <v>182</v>
+      </c>
+      <c r="H58" t="s">
+        <v>707</v>
+      </c>
+      <c r="J58" s="1" t="s">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" ht="28" x14ac:dyDescent="0.3">
+      <c r="A59" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="B58" t="s">
-        <v>608</v>
-      </c>
-      <c r="C58" t="s">
-        <v>729</v>
-      </c>
-      <c r="D58" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A59" s="2" t="s">
+      <c r="B59" t="s">
+        <v>602</v>
+      </c>
+      <c r="C59" t="s">
+        <v>718</v>
+      </c>
+      <c r="D59" t="s">
+        <v>23</v>
+      </c>
+      <c r="E59" t="s">
+        <v>888</v>
+      </c>
+      <c r="F59">
+        <v>58</v>
+      </c>
+      <c r="G59">
+        <v>178</v>
+      </c>
+      <c r="H59" t="s">
+        <v>35</v>
+      </c>
+      <c r="J59" s="1" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" ht="84" x14ac:dyDescent="0.3">
+      <c r="A60" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="B59" t="s">
-        <v>609</v>
-      </c>
-      <c r="C59" t="s">
-        <v>729</v>
-      </c>
-      <c r="D59" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A60" s="2" t="s">
-        <v>134</v>
-      </c>
       <c r="B60" t="s">
-        <v>610</v>
+        <v>603</v>
       </c>
       <c r="C60" t="s">
-        <v>729</v>
+        <v>718</v>
       </c>
       <c r="D60" t="s">
         <v>21</v>
       </c>
+      <c r="E60" t="s">
+        <v>875</v>
+      </c>
       <c r="F60">
         <v>27</v>
       </c>
       <c r="G60">
         <v>180</v>
       </c>
-    </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="H60" t="s">
+        <v>893</v>
+      </c>
+      <c r="J60" s="1" t="s">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" ht="28" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B61" t="s">
-        <v>822</v>
+        <v>808</v>
       </c>
       <c r="C61" t="s">
-        <v>729</v>
+        <v>718</v>
       </c>
       <c r="D61" t="s">
         <v>23</v>
       </c>
+      <c r="E61" t="s">
+        <v>874</v>
+      </c>
       <c r="F61">
         <v>23</v>
+      </c>
+      <c r="G61">
+        <v>183</v>
+      </c>
+      <c r="J61" s="1" t="s">
+        <v>894</v>
       </c>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B62" t="s">
-        <v>611</v>
+        <v>604</v>
       </c>
       <c r="C62" t="s">
-        <v>729</v>
+        <v>718</v>
       </c>
       <c r="D62" t="s">
         <v>21</v>
       </c>
       <c r="E62" t="s">
-        <v>783</v>
+        <v>771</v>
+      </c>
+      <c r="G62">
+        <v>175</v>
       </c>
       <c r="H62" t="s">
         <v>31</v>
       </c>
       <c r="J62" t="s">
-        <v>820</v>
+        <v>807</v>
       </c>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="B63" t="s">
+        <v>605</v>
+      </c>
+      <c r="C63" t="s">
+        <v>715</v>
+      </c>
+      <c r="D63" t="s">
+        <v>23</v>
+      </c>
+      <c r="E63" t="s">
+        <v>896</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11" ht="42" x14ac:dyDescent="0.3">
+      <c r="A64" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="B63" t="s">
-        <v>612</v>
-      </c>
-      <c r="C63" t="s">
-        <v>726</v>
-      </c>
-      <c r="D63" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A64" s="2" t="s">
-        <v>138</v>
-      </c>
       <c r="B64" t="s">
-        <v>613</v>
+        <v>606</v>
       </c>
       <c r="C64" t="s">
-        <v>726</v>
+        <v>715</v>
       </c>
       <c r="D64" t="s">
         <v>23</v>
       </c>
       <c r="E64" t="s">
-        <v>821</v>
-      </c>
-      <c r="J64" t="s">
-        <v>782</v>
+        <v>897</v>
+      </c>
+      <c r="G64">
+        <v>178</v>
+      </c>
+      <c r="J64" s="1" t="s">
+        <v>902</v>
       </c>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B65" t="s">
-        <v>614</v>
+        <v>607</v>
       </c>
       <c r="C65" t="s">
-        <v>726</v>
+        <v>715</v>
       </c>
       <c r="D65" t="s">
         <v>23</v>
+      </c>
+      <c r="E65" t="s">
+        <v>898</v>
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B66" t="s">
-        <v>615</v>
+        <v>608</v>
       </c>
       <c r="C66" t="s">
-        <v>726</v>
+        <v>715</v>
       </c>
       <c r="D66" t="s">
         <v>21</v>
       </c>
+      <c r="E66" t="s">
+        <v>898</v>
+      </c>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B67" t="s">
-        <v>616</v>
+        <v>609</v>
       </c>
       <c r="C67" t="s">
-        <v>726</v>
+        <v>715</v>
       </c>
       <c r="D67" t="s">
         <v>23</v>
+      </c>
+      <c r="E67" t="s">
+        <v>898</v>
       </c>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B68" t="s">
-        <v>617</v>
+        <v>610</v>
       </c>
       <c r="C68" t="s">
-        <v>726</v>
+        <v>715</v>
       </c>
       <c r="D68" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="E68" t="s">
+        <v>898</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" ht="28" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B69" t="s">
-        <v>618</v>
+        <v>611</v>
       </c>
       <c r="C69" t="s">
-        <v>726</v>
+        <v>715</v>
       </c>
       <c r="D69" t="s">
         <v>21</v>
       </c>
+      <c r="E69" t="s">
+        <v>899</v>
+      </c>
+      <c r="J69" s="1" t="s">
+        <v>900</v>
+      </c>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B70" t="s">
-        <v>619</v>
+        <v>612</v>
       </c>
       <c r="C70" t="s">
-        <v>726</v>
+        <v>715</v>
       </c>
       <c r="D70" t="s">
         <v>23</v>
+      </c>
+      <c r="E70" t="s">
+        <v>899</v>
+      </c>
+      <c r="J70" t="s">
+        <v>901</v>
       </c>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B71" t="s">
-        <v>620</v>
+        <v>613</v>
       </c>
       <c r="C71" t="s">
-        <v>726</v>
+        <v>715</v>
       </c>
       <c r="D71" t="s">
         <v>23</v>
+      </c>
+      <c r="E71" t="s">
+        <v>899</v>
+      </c>
+      <c r="J71" t="s">
+        <v>901</v>
       </c>
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B72" t="s">
-        <v>621</v>
+        <v>614</v>
       </c>
       <c r="C72" t="s">
-        <v>726</v>
+        <v>715</v>
       </c>
       <c r="D72" t="s">
         <v>23</v>
+      </c>
+      <c r="E72" t="s">
+        <v>899</v>
+      </c>
+      <c r="J72" t="s">
+        <v>881</v>
       </c>
     </row>
     <row r="73" spans="1:10" ht="56" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B73" t="s">
-        <v>622</v>
+        <v>615</v>
       </c>
       <c r="C73" t="s">
-        <v>730</v>
+        <v>719</v>
       </c>
       <c r="D73" t="s">
         <v>21</v>
       </c>
       <c r="E73" t="s">
-        <v>777</v>
+        <v>766</v>
       </c>
       <c r="F73" t="s">
-        <v>745</v>
+        <v>734</v>
       </c>
       <c r="G73">
         <v>180</v>
       </c>
       <c r="H73" t="s">
-        <v>730</v>
+        <v>719</v>
       </c>
       <c r="J73" s="1" t="s">
-        <v>760</v>
+        <v>749</v>
       </c>
     </row>
     <row r="74" spans="1:10" ht="98" x14ac:dyDescent="0.3">
       <c r="A74" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B74" t="s">
-        <v>624</v>
+        <v>617</v>
       </c>
       <c r="C74" t="s">
-        <v>730</v>
+        <v>719</v>
       </c>
       <c r="D74" t="s">
         <v>21</v>
       </c>
       <c r="E74" t="s">
-        <v>779</v>
+        <v>768</v>
       </c>
       <c r="F74" t="s">
-        <v>746</v>
+        <v>735</v>
       </c>
       <c r="G74">
         <v>168</v>
       </c>
       <c r="H74" t="s">
-        <v>804</v>
+        <v>791</v>
       </c>
       <c r="J74" s="1" t="s">
-        <v>763</v>
+        <v>752</v>
       </c>
     </row>
     <row r="75" spans="1:10" ht="56" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B75" t="s">
-        <v>625</v>
+        <v>618</v>
       </c>
       <c r="C75" t="s">
-        <v>730</v>
+        <v>719</v>
       </c>
       <c r="D75" t="s">
         <v>21</v>
       </c>
       <c r="E75" t="s">
-        <v>776</v>
+        <v>765</v>
       </c>
       <c r="F75" t="s">
-        <v>751</v>
+        <v>740</v>
       </c>
       <c r="G75">
         <v>170</v>
       </c>
       <c r="H75" t="s">
-        <v>730</v>
+        <v>719</v>
       </c>
       <c r="J75" s="1" t="s">
-        <v>764</v>
+        <v>753</v>
       </c>
     </row>
     <row r="76" spans="1:10" ht="56" x14ac:dyDescent="0.3">
       <c r="A76" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B76" t="s">
-        <v>626</v>
+        <v>619</v>
       </c>
       <c r="C76" t="s">
-        <v>730</v>
+        <v>719</v>
       </c>
       <c r="D76" t="s">
         <v>21</v>
       </c>
       <c r="E76" t="s">
-        <v>775</v>
+        <v>764</v>
       </c>
       <c r="F76" t="s">
-        <v>750</v>
+        <v>739</v>
       </c>
       <c r="G76">
         <v>178</v>
       </c>
       <c r="H76" t="s">
-        <v>730</v>
+        <v>719</v>
       </c>
       <c r="J76" s="1" t="s">
-        <v>765</v>
+        <v>754</v>
       </c>
     </row>
     <row r="77" spans="1:10" ht="28" x14ac:dyDescent="0.3">
       <c r="A77" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B77" t="s">
-        <v>627</v>
+        <v>620</v>
       </c>
       <c r="C77" t="s">
-        <v>730</v>
+        <v>719</v>
       </c>
       <c r="D77" t="s">
         <v>21</v>
       </c>
       <c r="E77" t="s">
-        <v>774</v>
+        <v>763</v>
       </c>
       <c r="F77" t="s">
-        <v>750</v>
+        <v>739</v>
       </c>
       <c r="G77">
         <v>160</v>
       </c>
       <c r="H77" t="s">
-        <v>730</v>
+        <v>719</v>
       </c>
       <c r="J77" s="1" t="s">
-        <v>762</v>
+        <v>751</v>
       </c>
     </row>
     <row r="78" spans="1:10" ht="56" x14ac:dyDescent="0.3">
       <c r="A78" s="2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B78" t="s">
-        <v>628</v>
+        <v>621</v>
       </c>
       <c r="C78" t="s">
-        <v>730</v>
+        <v>719</v>
       </c>
       <c r="D78" t="s">
         <v>21</v>
       </c>
       <c r="E78" t="s">
-        <v>773</v>
+        <v>762</v>
       </c>
       <c r="F78" t="s">
-        <v>752</v>
+        <v>741</v>
       </c>
       <c r="G78">
         <v>155</v>
       </c>
       <c r="H78" t="s">
-        <v>730</v>
+        <v>719</v>
       </c>
       <c r="J78" s="1" t="s">
-        <v>766</v>
+        <v>755</v>
       </c>
     </row>
     <row r="79" spans="1:10" ht="28" x14ac:dyDescent="0.3">
       <c r="A79" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B79" t="s">
-        <v>629</v>
+        <v>622</v>
       </c>
       <c r="C79" t="s">
-        <v>730</v>
+        <v>719</v>
       </c>
       <c r="D79" t="s">
         <v>23</v>
       </c>
       <c r="E79" t="s">
-        <v>772</v>
+        <v>761</v>
       </c>
       <c r="F79" t="s">
-        <v>752</v>
+        <v>741</v>
       </c>
       <c r="H79" t="s">
-        <v>805</v>
+        <v>792</v>
       </c>
       <c r="J79" s="1" t="s">
-        <v>768</v>
+        <v>757</v>
       </c>
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A80" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B80" t="s">
-        <v>623</v>
+        <v>616</v>
       </c>
       <c r="C80" t="s">
-        <v>730</v>
+        <v>719</v>
       </c>
       <c r="D80" t="s">
         <v>21</v>
       </c>
       <c r="E80" t="s">
-        <v>770</v>
+        <v>759</v>
       </c>
       <c r="F80" t="s">
-        <v>753</v>
+        <v>742</v>
       </c>
       <c r="G80">
         <v>190</v>
       </c>
       <c r="H80" t="s">
-        <v>730</v>
+        <v>719</v>
       </c>
       <c r="J80" s="1" t="s">
-        <v>769</v>
+        <v>758</v>
       </c>
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A81" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B81" t="s">
-        <v>755</v>
+        <v>744</v>
       </c>
       <c r="C81" t="s">
-        <v>730</v>
+        <v>719</v>
       </c>
       <c r="D81" t="s">
         <v>21</v>
       </c>
       <c r="F81" t="s">
-        <v>756</v>
+        <v>745</v>
       </c>
       <c r="H81" t="s">
-        <v>730</v>
+        <v>719</v>
       </c>
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A82" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B82" t="s">
-        <v>754</v>
+        <v>743</v>
       </c>
       <c r="C82" t="s">
-        <v>730</v>
+        <v>719</v>
       </c>
       <c r="D82" t="s">
         <v>21</v>
       </c>
       <c r="F82" t="s">
-        <v>756</v>
+        <v>745</v>
       </c>
       <c r="H82" t="s">
-        <v>730</v>
+        <v>719</v>
       </c>
     </row>
     <row r="83" spans="1:10" ht="70" x14ac:dyDescent="0.3">
       <c r="A83" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B83" t="s">
-        <v>630</v>
+        <v>623</v>
       </c>
       <c r="C83" t="s">
-        <v>731</v>
+        <v>720</v>
       </c>
       <c r="D83" t="s">
         <v>23</v>
       </c>
       <c r="E83" t="s">
-        <v>771</v>
+        <v>760</v>
       </c>
       <c r="F83" t="s">
-        <v>744</v>
+        <v>733</v>
       </c>
       <c r="G83">
         <v>181</v>
       </c>
       <c r="H83" t="s">
-        <v>731</v>
+        <v>720</v>
       </c>
       <c r="J83" s="1" t="s">
-        <v>781</v>
+        <v>770</v>
       </c>
     </row>
     <row r="84" spans="1:10" ht="42" x14ac:dyDescent="0.3">
       <c r="A84" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B84" t="s">
-        <v>631</v>
+        <v>624</v>
       </c>
       <c r="C84" t="s">
-        <v>731</v>
+        <v>720</v>
       </c>
       <c r="D84" t="s">
         <v>23</v>
       </c>
       <c r="E84" t="s">
-        <v>778</v>
+        <v>767</v>
       </c>
       <c r="F84" t="s">
-        <v>749</v>
+        <v>738</v>
       </c>
       <c r="G84">
         <v>180</v>
       </c>
       <c r="H84" t="s">
-        <v>804</v>
+        <v>791</v>
       </c>
       <c r="J84" s="1" t="s">
-        <v>799</v>
+        <v>786</v>
       </c>
     </row>
     <row r="85" spans="1:10" ht="70" x14ac:dyDescent="0.3">
       <c r="A85" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B85" t="s">
-        <v>632</v>
+        <v>625</v>
       </c>
       <c r="C85" t="s">
-        <v>731</v>
+        <v>720</v>
       </c>
       <c r="D85" t="s">
         <v>23</v>
       </c>
       <c r="E85" t="s">
-        <v>780</v>
+        <v>769</v>
       </c>
       <c r="F85" t="s">
-        <v>746</v>
+        <v>735</v>
       </c>
       <c r="G85">
         <v>177</v>
       </c>
       <c r="H85" t="s">
-        <v>804</v>
+        <v>791</v>
       </c>
       <c r="J85" s="1" t="s">
-        <v>784</v>
+        <v>772</v>
       </c>
     </row>
     <row r="86" spans="1:10" ht="70" x14ac:dyDescent="0.3">
       <c r="A86" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B86" t="s">
-        <v>633</v>
+        <v>626</v>
       </c>
       <c r="C86" t="s">
-        <v>731</v>
+        <v>720</v>
       </c>
       <c r="D86" t="s">
         <v>23</v>
       </c>
       <c r="E86" t="s">
-        <v>786</v>
+        <v>774</v>
       </c>
       <c r="F86" t="s">
-        <v>750</v>
+        <v>739</v>
       </c>
       <c r="G86">
         <v>178</v>
       </c>
       <c r="H86" t="s">
-        <v>731</v>
+        <v>720</v>
       </c>
       <c r="J86" s="1" t="s">
-        <v>785</v>
+        <v>773</v>
       </c>
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A87" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B87" t="s">
-        <v>634</v>
+        <v>627</v>
       </c>
       <c r="C87" t="s">
-        <v>731</v>
+        <v>720</v>
       </c>
       <c r="D87" t="s">
         <v>23</v>
       </c>
       <c r="H87" t="s">
-        <v>731</v>
+        <v>720</v>
       </c>
     </row>
     <row r="88" spans="1:10" ht="84" x14ac:dyDescent="0.3">
       <c r="A88" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B88" t="s">
-        <v>727</v>
+        <v>716</v>
       </c>
       <c r="C88" t="s">
-        <v>731</v>
+        <v>720</v>
       </c>
       <c r="D88" t="s">
         <v>23</v>
       </c>
       <c r="E88" t="s">
-        <v>787</v>
+        <v>775</v>
       </c>
       <c r="F88">
         <v>23</v>
       </c>
       <c r="G88" t="s">
-        <v>789</v>
+        <v>777</v>
       </c>
       <c r="H88" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="J88" s="1" t="s">
-        <v>792</v>
+        <v>780</v>
       </c>
     </row>
     <row r="89" spans="1:10" ht="84" x14ac:dyDescent="0.3">
       <c r="A89" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B89" t="s">
-        <v>635</v>
+        <v>628</v>
       </c>
       <c r="C89" t="s">
-        <v>732</v>
+        <v>721</v>
       </c>
       <c r="D89" t="s">
         <v>23</v>
       </c>
       <c r="E89" t="s">
-        <v>794</v>
+        <v>781</v>
       </c>
       <c r="F89" t="s">
-        <v>747</v>
+        <v>736</v>
       </c>
       <c r="G89">
         <v>210</v>
       </c>
       <c r="H89" t="s">
-        <v>732</v>
+        <v>721</v>
       </c>
       <c r="J89" s="1" t="s">
-        <v>796</v>
+        <v>783</v>
       </c>
     </row>
     <row r="90" spans="1:10" ht="28" x14ac:dyDescent="0.3">
       <c r="A90" s="2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B90" t="s">
-        <v>636</v>
+        <v>629</v>
       </c>
       <c r="C90" t="s">
-        <v>732</v>
+        <v>721</v>
       </c>
       <c r="D90" t="s">
         <v>23</v>
       </c>
       <c r="E90" t="s">
-        <v>797</v>
+        <v>784</v>
       </c>
       <c r="F90" t="s">
-        <v>747</v>
+        <v>736</v>
       </c>
       <c r="G90">
         <v>190</v>
       </c>
       <c r="H90" t="s">
-        <v>804</v>
+        <v>791</v>
       </c>
       <c r="J90" s="1" t="s">
-        <v>800</v>
+        <v>787</v>
       </c>
     </row>
     <row r="91" spans="1:10" ht="84" x14ac:dyDescent="0.3">
       <c r="A91" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B91" t="s">
-        <v>637</v>
+        <v>630</v>
       </c>
       <c r="C91" t="s">
-        <v>732</v>
+        <v>721</v>
       </c>
       <c r="D91" t="s">
         <v>21</v>
       </c>
       <c r="E91" t="s">
-        <v>798</v>
+        <v>785</v>
       </c>
       <c r="F91" t="s">
-        <v>746</v>
+        <v>735</v>
       </c>
       <c r="G91">
         <v>175</v>
       </c>
       <c r="H91" t="s">
-        <v>804</v>
+        <v>791</v>
       </c>
       <c r="J91" s="1" t="s">
-        <v>801</v>
+        <v>788</v>
       </c>
     </row>
     <row r="92" spans="1:10" ht="42" x14ac:dyDescent="0.3">
       <c r="A92" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B92" t="s">
-        <v>638</v>
+        <v>631</v>
       </c>
       <c r="C92" t="s">
-        <v>732</v>
+        <v>721</v>
       </c>
       <c r="D92" t="s">
         <v>23</v>
       </c>
       <c r="E92" t="s">
-        <v>803</v>
+        <v>790</v>
       </c>
       <c r="H92" t="s">
-        <v>806</v>
+        <v>793</v>
       </c>
       <c r="J92" s="1" t="s">
-        <v>802</v>
+        <v>789</v>
       </c>
     </row>
     <row r="93" spans="1:10" ht="42" x14ac:dyDescent="0.3">
       <c r="A93" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B93" t="s">
-        <v>639</v>
+        <v>632</v>
       </c>
       <c r="C93" t="s">
-        <v>732</v>
+        <v>721</v>
       </c>
       <c r="D93" t="s">
         <v>23</v>
       </c>
       <c r="E93" t="s">
-        <v>807</v>
+        <v>794</v>
       </c>
       <c r="F93" t="s">
-        <v>752</v>
+        <v>741</v>
       </c>
       <c r="G93">
         <v>160</v>
       </c>
       <c r="H93" t="s">
-        <v>732</v>
+        <v>721</v>
       </c>
       <c r="J93" s="1" t="s">
-        <v>811</v>
+        <v>799</v>
       </c>
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A94" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B94" t="s">
-        <v>640</v>
+        <v>633</v>
       </c>
       <c r="C94" t="s">
-        <v>732</v>
+        <v>721</v>
       </c>
       <c r="D94" t="s">
         <v>21</v>
       </c>
       <c r="H94" t="s">
-        <v>732</v>
+        <v>721</v>
       </c>
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A95" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B95" t="s">
-        <v>641</v>
+        <v>634</v>
       </c>
       <c r="C95" t="s">
-        <v>732</v>
+        <v>721</v>
       </c>
       <c r="D95" t="s">
         <v>23</v>
       </c>
       <c r="H95" t="s">
-        <v>732</v>
+        <v>721</v>
       </c>
     </row>
     <row r="96" spans="1:10" ht="84" x14ac:dyDescent="0.3">
       <c r="A96" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B96" t="s">
-        <v>642</v>
+        <v>635</v>
       </c>
       <c r="C96" t="s">
-        <v>733</v>
+        <v>722</v>
       </c>
       <c r="D96" t="s">
         <v>23</v>
       </c>
       <c r="E96" t="s">
-        <v>795</v>
+        <v>782</v>
       </c>
       <c r="F96" t="s">
-        <v>748</v>
+        <v>737</v>
       </c>
       <c r="G96">
         <v>180</v>
       </c>
       <c r="H96" t="s">
-        <v>733</v>
+        <v>722</v>
       </c>
       <c r="J96" s="1" t="s">
-        <v>812</v>
+        <v>800</v>
       </c>
     </row>
     <row r="97" spans="1:10" ht="84" x14ac:dyDescent="0.3">
       <c r="A97" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B97" t="s">
-        <v>643</v>
+        <v>636</v>
       </c>
       <c r="C97" t="s">
-        <v>733</v>
+        <v>722</v>
       </c>
       <c r="D97" t="s">
         <v>23</v>
       </c>
       <c r="E97" t="s">
-        <v>808</v>
+        <v>796</v>
       </c>
       <c r="F97" t="s">
-        <v>746</v>
+        <v>735</v>
       </c>
       <c r="G97">
         <v>177</v>
       </c>
       <c r="H97" t="s">
-        <v>804</v>
+        <v>791</v>
       </c>
       <c r="J97" s="1" t="s">
-        <v>813</v>
+        <v>802</v>
       </c>
     </row>
     <row r="98" spans="1:10" ht="28" x14ac:dyDescent="0.3">
       <c r="A98" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B98" t="s">
-        <v>644</v>
+        <v>637</v>
       </c>
       <c r="C98" t="s">
-        <v>733</v>
+        <v>722</v>
       </c>
       <c r="D98" t="s">
         <v>21</v>
       </c>
       <c r="E98" t="s">
-        <v>810</v>
+        <v>798</v>
       </c>
       <c r="F98" t="s">
-        <v>752</v>
+        <v>741</v>
       </c>
       <c r="G98">
         <v>158</v>
       </c>
       <c r="H98" t="s">
-        <v>733</v>
+        <v>722</v>
       </c>
       <c r="J98" s="1" t="s">
-        <v>814</v>
+        <v>803</v>
       </c>
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A99" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B99" t="s">
-        <v>645</v>
+        <v>638</v>
       </c>
       <c r="C99" t="s">
-        <v>733</v>
+        <v>722</v>
       </c>
       <c r="D99" t="s">
         <v>21</v>
       </c>
       <c r="E99" t="s">
-        <v>809</v>
+        <v>797</v>
       </c>
       <c r="F99" t="s">
-        <v>752</v>
+        <v>741</v>
       </c>
       <c r="G99">
         <v>163</v>
       </c>
       <c r="H99" t="s">
-        <v>733</v>
+        <v>722</v>
+      </c>
+      <c r="J99" t="s">
+        <v>801</v>
       </c>
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A100" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="B100" t="s">
+        <v>639</v>
+      </c>
+      <c r="C100" t="s">
+        <v>722</v>
+      </c>
+      <c r="D100" t="s">
+        <v>23</v>
+      </c>
+      <c r="J100" t="s">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="101" spans="1:10" ht="28" x14ac:dyDescent="0.3">
+      <c r="A101" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="B100" t="s">
-        <v>646</v>
-      </c>
-      <c r="C100" t="s">
-        <v>733</v>
-      </c>
-      <c r="D100" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="101" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A101" s="2" t="s">
-        <v>175</v>
-      </c>
       <c r="B101" t="s">
-        <v>648</v>
+        <v>641</v>
       </c>
       <c r="C101" t="s">
-        <v>733</v>
+        <v>722</v>
       </c>
       <c r="D101" t="s">
         <v>23</v>
       </c>
       <c r="E101" t="s">
-        <v>815</v>
+        <v>804</v>
       </c>
       <c r="F101" t="s">
-        <v>748</v>
+        <v>737</v>
       </c>
       <c r="G101">
         <v>186</v>
       </c>
       <c r="H101" t="s">
-        <v>733</v>
-      </c>
-    </row>
-    <row r="102" spans="1:10" x14ac:dyDescent="0.3">
+        <v>722</v>
+      </c>
+      <c r="J101" s="1" t="s">
+        <v>865</v>
+      </c>
+    </row>
+    <row r="102" spans="1:10" ht="28" x14ac:dyDescent="0.3">
       <c r="A102" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B102" t="s">
-        <v>647</v>
+        <v>640</v>
       </c>
       <c r="C102" t="s">
-        <v>733</v>
+        <v>722</v>
       </c>
       <c r="D102" t="s">
         <v>21</v>
       </c>
       <c r="E102" t="s">
-        <v>816</v>
+        <v>805</v>
       </c>
       <c r="F102" t="s">
-        <v>748</v>
+        <v>737</v>
       </c>
       <c r="G102">
         <v>186</v>
       </c>
       <c r="H102" t="s">
-        <v>733</v>
+        <v>722</v>
+      </c>
+      <c r="J102" s="1" t="s">
+        <v>866</v>
       </c>
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A103" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B103" t="s">
-        <v>709</v>
+        <v>702</v>
       </c>
       <c r="C103" t="s">
-        <v>733</v>
+        <v>722</v>
       </c>
       <c r="D103" t="s">
         <v>23</v>
       </c>
       <c r="E103" t="s">
-        <v>817</v>
+        <v>806</v>
+      </c>
+      <c r="F103" t="s">
+        <v>795</v>
+      </c>
+      <c r="G103">
+        <v>169</v>
+      </c>
+      <c r="H103" t="s">
+        <v>722</v>
+      </c>
+      <c r="J103" s="1" t="s">
+        <v>867</v>
       </c>
     </row>
     <row r="104" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A104" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="B104" t="s">
+        <v>642</v>
+      </c>
+      <c r="C104" t="s">
+        <v>723</v>
+      </c>
+      <c r="D104" t="s">
+        <v>23</v>
+      </c>
+      <c r="E104" t="s">
+        <v>820</v>
+      </c>
+      <c r="F104" t="s">
+        <v>733</v>
+      </c>
+      <c r="G104">
+        <v>176</v>
+      </c>
+      <c r="J104" s="1" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="105" spans="1:10" ht="70" x14ac:dyDescent="0.3">
+      <c r="A105" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="B104" t="s">
-        <v>649</v>
-      </c>
-      <c r="C104" t="s">
-        <v>734</v>
-      </c>
-      <c r="D104" t="s">
-        <v>23</v>
-      </c>
-      <c r="E104" t="s">
-        <v>834</v>
-      </c>
-      <c r="J104" s="1" t="s">
-        <v>833</v>
-      </c>
-    </row>
-    <row r="105" spans="1:10" ht="56" x14ac:dyDescent="0.3">
-      <c r="A105" s="2" t="s">
-        <v>179</v>
-      </c>
       <c r="B105" t="s">
-        <v>650</v>
+        <v>643</v>
       </c>
       <c r="C105" t="s">
-        <v>734</v>
+        <v>723</v>
       </c>
       <c r="D105" t="s">
         <v>21</v>
       </c>
       <c r="E105" t="s">
-        <v>835</v>
+        <v>821</v>
+      </c>
+      <c r="F105" t="s">
+        <v>733</v>
+      </c>
+      <c r="G105">
+        <v>164</v>
+      </c>
+      <c r="H105" t="s">
+        <v>868</v>
       </c>
       <c r="J105" s="1" t="s">
-        <v>842</v>
-      </c>
-    </row>
-    <row r="106" spans="1:10" ht="70" x14ac:dyDescent="0.3">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="106" spans="1:10" ht="84" x14ac:dyDescent="0.3">
       <c r="A106" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B106" t="s">
-        <v>651</v>
+        <v>644</v>
       </c>
       <c r="C106" t="s">
-        <v>734</v>
+        <v>723</v>
       </c>
       <c r="D106" t="s">
         <v>23</v>
       </c>
       <c r="E106" t="s">
-        <v>836</v>
+        <v>822</v>
+      </c>
+      <c r="F106" t="s">
+        <v>733</v>
+      </c>
+      <c r="G106">
+        <v>185</v>
+      </c>
+      <c r="H106" t="s">
+        <v>868</v>
       </c>
       <c r="J106" s="1" t="s">
-        <v>837</v>
+        <v>860</v>
       </c>
     </row>
     <row r="107" spans="1:10" ht="28" x14ac:dyDescent="0.3">
       <c r="A107" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B107" t="s">
-        <v>652</v>
+        <v>645</v>
       </c>
       <c r="C107" t="s">
-        <v>734</v>
+        <v>723</v>
       </c>
       <c r="D107" t="s">
         <v>23</v>
       </c>
       <c r="E107" t="s">
-        <v>838</v>
+        <v>823</v>
+      </c>
+      <c r="F107" t="s">
+        <v>733</v>
+      </c>
+      <c r="G107">
+        <v>182</v>
+      </c>
+      <c r="H107" t="s">
+        <v>868</v>
       </c>
       <c r="J107" s="1" t="s">
-        <v>839</v>
+        <v>824</v>
       </c>
     </row>
     <row r="108" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A108" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B108" t="s">
-        <v>653</v>
+        <v>646</v>
       </c>
       <c r="C108" t="s">
-        <v>734</v>
+        <v>723</v>
       </c>
       <c r="D108" t="s">
         <v>21</v>
       </c>
       <c r="E108" t="s">
-        <v>840</v>
+        <v>825</v>
+      </c>
+      <c r="F108" t="s">
+        <v>733</v>
+      </c>
+      <c r="G108">
+        <v>166</v>
+      </c>
+      <c r="H108" t="s">
+        <v>868</v>
       </c>
       <c r="J108" s="1" t="s">
-        <v>841</v>
-      </c>
-    </row>
-    <row r="109" spans="1:10" x14ac:dyDescent="0.3">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="109" spans="1:10" ht="112" x14ac:dyDescent="0.3">
       <c r="A109" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B109" t="s">
-        <v>654</v>
+        <v>647</v>
       </c>
       <c r="C109" t="s">
-        <v>734</v>
+        <v>723</v>
       </c>
       <c r="D109" t="s">
         <v>23</v>
       </c>
-      <c r="J109" t="s">
-        <v>818</v>
-      </c>
-    </row>
-    <row r="110" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="E109" t="s">
+        <v>847</v>
+      </c>
+      <c r="F109" t="s">
+        <v>740</v>
+      </c>
+      <c r="G109">
+        <v>187</v>
+      </c>
+      <c r="H109" t="s">
+        <v>868</v>
+      </c>
+      <c r="J109" s="1" t="s">
+        <v>854</v>
+      </c>
+    </row>
+    <row r="110" spans="1:10" ht="84" x14ac:dyDescent="0.3">
       <c r="A110" s="2" t="s">
-        <v>657</v>
+        <v>650</v>
       </c>
       <c r="B110" t="s">
-        <v>655</v>
+        <v>648</v>
       </c>
       <c r="C110" t="s">
-        <v>734</v>
+        <v>723</v>
       </c>
       <c r="D110" t="s">
         <v>21</v>
       </c>
-      <c r="J110" t="s">
-        <v>819</v>
-      </c>
-    </row>
-    <row r="111" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="E110" t="s">
+        <v>846</v>
+      </c>
+      <c r="F110" t="s">
+        <v>739</v>
+      </c>
+      <c r="G110">
+        <v>175</v>
+      </c>
+      <c r="H110" t="s">
+        <v>868</v>
+      </c>
+      <c r="J110" s="1" t="s">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="111" spans="1:10" ht="42" x14ac:dyDescent="0.3">
       <c r="A111" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="B111" t="s">
+        <v>649</v>
+      </c>
+      <c r="C111" t="s">
+        <v>723</v>
+      </c>
+      <c r="D111" t="s">
+        <v>23</v>
+      </c>
+      <c r="E111" t="s">
+        <v>843</v>
+      </c>
+      <c r="F111" t="s">
+        <v>741</v>
+      </c>
+      <c r="G111">
+        <v>180</v>
+      </c>
+      <c r="H111" t="s">
+        <v>868</v>
+      </c>
+      <c r="J111" s="1" t="s">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="112" spans="1:10" ht="42" x14ac:dyDescent="0.3">
+      <c r="A112" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="B111" t="s">
-        <v>656</v>
-      </c>
-      <c r="C111" t="s">
-        <v>734</v>
-      </c>
-      <c r="D111" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="112" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A112" s="2" t="s">
+      <c r="B112" t="s">
+        <v>651</v>
+      </c>
+      <c r="C112" t="s">
+        <v>723</v>
+      </c>
+      <c r="D112" t="s">
+        <v>23</v>
+      </c>
+      <c r="E112" t="s">
+        <v>845</v>
+      </c>
+      <c r="F112">
+        <v>32</v>
+      </c>
+      <c r="G112">
+        <v>188</v>
+      </c>
+      <c r="H112" t="s">
+        <v>868</v>
+      </c>
+      <c r="J112" s="1" t="s">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="113" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A113" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="B112" t="s">
-        <v>658</v>
-      </c>
-      <c r="C112" t="s">
-        <v>734</v>
-      </c>
-      <c r="D112" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A113" s="2" t="s">
+      <c r="B113" t="s">
+        <v>652</v>
+      </c>
+      <c r="C113" t="s">
+        <v>723</v>
+      </c>
+      <c r="D113" t="s">
+        <v>23</v>
+      </c>
+      <c r="E113" t="s">
+        <v>848</v>
+      </c>
+      <c r="F113" t="s">
+        <v>739</v>
+      </c>
+      <c r="H113" t="s">
+        <v>868</v>
+      </c>
+      <c r="J113" s="1" t="s">
+        <v>852</v>
+      </c>
+    </row>
+    <row r="114" spans="1:10" ht="28" x14ac:dyDescent="0.3">
+      <c r="A114" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="B113" t="s">
-        <v>659</v>
-      </c>
-      <c r="C113" t="s">
-        <v>734</v>
-      </c>
-      <c r="D113" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A114" s="2" t="s">
+      <c r="B114" t="s">
+        <v>653</v>
+      </c>
+      <c r="C114" t="s">
+        <v>723</v>
+      </c>
+      <c r="D114" t="s">
+        <v>23</v>
+      </c>
+      <c r="E114" t="s">
+        <v>849</v>
+      </c>
+      <c r="F114" t="s">
+        <v>741</v>
+      </c>
+      <c r="H114" t="s">
+        <v>868</v>
+      </c>
+      <c r="J114" s="1" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="115" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A115" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="B114" t="s">
-        <v>660</v>
-      </c>
-      <c r="C114" t="s">
-        <v>734</v>
-      </c>
-      <c r="D114" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A115" s="2" t="s">
-        <v>188</v>
-      </c>
       <c r="B115" t="s">
-        <v>661</v>
+        <v>654</v>
       </c>
       <c r="C115" t="s">
-        <v>734</v>
+        <v>723</v>
       </c>
       <c r="D115" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E115" t="s">
+        <v>857</v>
+      </c>
+      <c r="F115" t="s">
+        <v>741</v>
+      </c>
+      <c r="H115" t="s">
+        <v>868</v>
+      </c>
+      <c r="J115" t="s">
+        <v>859</v>
+      </c>
+    </row>
+    <row r="116" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A116" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="B116" t="s">
+        <v>655</v>
+      </c>
+      <c r="C116" t="s">
+        <v>723</v>
+      </c>
+      <c r="D116" t="s">
+        <v>23</v>
+      </c>
+      <c r="E116" t="s">
+        <v>850</v>
+      </c>
+      <c r="F116" t="s">
+        <v>739</v>
+      </c>
+      <c r="H116" t="s">
+        <v>868</v>
+      </c>
+      <c r="J116" t="s">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="117" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A117" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="B116" t="s">
-        <v>662</v>
-      </c>
-      <c r="C116" t="s">
-        <v>734</v>
-      </c>
-      <c r="D116" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A117" s="2" t="s">
+      <c r="B117" t="s">
+        <v>656</v>
+      </c>
+      <c r="C117" t="s">
+        <v>723</v>
+      </c>
+      <c r="D117" t="s">
+        <v>23</v>
+      </c>
+      <c r="E117" t="s">
+        <v>857</v>
+      </c>
+      <c r="F117" t="s">
+        <v>740</v>
+      </c>
+      <c r="H117" t="s">
+        <v>868</v>
+      </c>
+      <c r="J117" t="s">
+        <v>859</v>
+      </c>
+    </row>
+    <row r="118" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A118" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="B117" t="s">
-        <v>663</v>
-      </c>
-      <c r="C117" t="s">
-        <v>734</v>
-      </c>
-      <c r="D117" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A118" s="2" t="s">
+      <c r="B118" t="s">
+        <v>657</v>
+      </c>
+      <c r="C118" t="s">
+        <v>723</v>
+      </c>
+      <c r="D118" t="s">
+        <v>23</v>
+      </c>
+      <c r="E118" t="s">
+        <v>851</v>
+      </c>
+      <c r="F118" t="s">
+        <v>795</v>
+      </c>
+      <c r="H118" t="s">
+        <v>868</v>
+      </c>
+      <c r="J118" t="s">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="119" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A119" s="2" t="s">
+        <v>660</v>
+      </c>
+      <c r="B119" t="s">
+        <v>659</v>
+      </c>
+      <c r="C119" t="s">
+        <v>723</v>
+      </c>
+      <c r="D119" t="s">
+        <v>23</v>
+      </c>
+      <c r="E119" t="s">
+        <v>851</v>
+      </c>
+      <c r="F119" t="s">
+        <v>795</v>
+      </c>
+      <c r="H119" t="s">
+        <v>868</v>
+      </c>
+      <c r="J119" t="s">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="120" spans="1:10" ht="28" x14ac:dyDescent="0.3">
+      <c r="A120" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="B118" t="s">
-        <v>664</v>
-      </c>
-      <c r="C118" t="s">
-        <v>734</v>
-      </c>
-      <c r="D118" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A119" s="2" t="s">
-        <v>667</v>
-      </c>
-      <c r="B119" t="s">
-        <v>666</v>
-      </c>
-      <c r="C119" t="s">
-        <v>734</v>
-      </c>
-      <c r="D119" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A120" s="2" t="s">
-        <v>192</v>
-      </c>
       <c r="B120" t="s">
-        <v>665</v>
+        <v>658</v>
       </c>
       <c r="C120" t="s">
-        <v>734</v>
+        <v>723</v>
       </c>
       <c r="D120" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E120" t="s">
+        <v>863</v>
+      </c>
+      <c r="F120" t="s">
+        <v>795</v>
+      </c>
+      <c r="H120" t="s">
+        <v>868</v>
+      </c>
+      <c r="J120" s="1" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="121" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A121" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="B121" t="s">
+        <v>661</v>
+      </c>
+      <c r="C121" t="s">
+        <v>724</v>
+      </c>
+      <c r="D121" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="122" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A122" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="B121" t="s">
-        <v>668</v>
-      </c>
-      <c r="C121" t="s">
-        <v>735</v>
-      </c>
-      <c r="D121" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A122" s="2" t="s">
-        <v>194</v>
-      </c>
       <c r="B122" t="s">
-        <v>670</v>
+        <v>663</v>
       </c>
       <c r="C122" t="s">
-        <v>735</v>
+        <v>724</v>
       </c>
       <c r="D122" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A123" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B123" t="s">
-        <v>675</v>
+        <v>668</v>
       </c>
       <c r="C123" t="s">
-        <v>735</v>
+        <v>724</v>
       </c>
       <c r="D123" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A124" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="B124" t="s">
+        <v>662</v>
+      </c>
+      <c r="C124" t="s">
+        <v>724</v>
+      </c>
+      <c r="D124" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="125" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A125" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="B124" t="s">
-        <v>669</v>
-      </c>
-      <c r="C124" t="s">
-        <v>735</v>
-      </c>
-      <c r="D124" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A125" s="2" t="s">
+      <c r="B125" t="s">
+        <v>664</v>
+      </c>
+      <c r="C125" t="s">
+        <v>724</v>
+      </c>
+      <c r="D125" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="126" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A126" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="B125" t="s">
-        <v>671</v>
-      </c>
-      <c r="C125" t="s">
-        <v>735</v>
-      </c>
-      <c r="D125" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A126" s="2" t="s">
-        <v>198</v>
-      </c>
       <c r="B126" t="s">
-        <v>672</v>
+        <v>665</v>
       </c>
       <c r="C126" t="s">
-        <v>735</v>
+        <v>724</v>
       </c>
       <c r="D126" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A127" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="B127" t="s">
+        <v>666</v>
+      </c>
+      <c r="C127" t="s">
+        <v>724</v>
+      </c>
+      <c r="D127" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="128" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A128" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="B127" t="s">
-        <v>673</v>
-      </c>
-      <c r="C127" t="s">
-        <v>735</v>
-      </c>
-      <c r="D127" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A128" s="2" t="s">
-        <v>200</v>
-      </c>
       <c r="B128" t="s">
-        <v>674</v>
+        <v>667</v>
       </c>
       <c r="C128" t="s">
-        <v>735</v>
+        <v>724</v>
       </c>
       <c r="D128" t="s">
         <v>23</v>
@@ -6941,13 +7598,13 @@
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A129" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B129" t="s">
-        <v>676</v>
+        <v>669</v>
       </c>
       <c r="C129" t="s">
-        <v>736</v>
+        <v>725</v>
       </c>
       <c r="D129" t="s">
         <v>21</v>
@@ -6955,13 +7612,13 @@
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A130" s="2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B130" t="s">
-        <v>677</v>
+        <v>670</v>
       </c>
       <c r="C130" t="s">
-        <v>736</v>
+        <v>725</v>
       </c>
       <c r="D130" t="s">
         <v>23</v>
@@ -6969,13 +7626,13 @@
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A131" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B131" t="s">
-        <v>678</v>
+        <v>671</v>
       </c>
       <c r="C131" t="s">
-        <v>736</v>
+        <v>725</v>
       </c>
       <c r="D131" t="s">
         <v>21</v>
@@ -6983,13 +7640,13 @@
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A132" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B132" t="s">
-        <v>679</v>
+        <v>672</v>
       </c>
       <c r="C132" t="s">
-        <v>736</v>
+        <v>725</v>
       </c>
       <c r="D132" t="s">
         <v>23</v>
@@ -6997,13 +7654,13 @@
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A133" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B133" t="s">
-        <v>680</v>
+        <v>673</v>
       </c>
       <c r="C133" t="s">
-        <v>736</v>
+        <v>725</v>
       </c>
       <c r="D133" t="s">
         <v>21</v>
@@ -7011,13 +7668,13 @@
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A134" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B134" t="s">
-        <v>686</v>
+        <v>679</v>
       </c>
       <c r="C134" t="s">
-        <v>736</v>
+        <v>725</v>
       </c>
       <c r="D134" t="s">
         <v>23</v>
@@ -7025,13 +7682,13 @@
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A135" s="2" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B135" t="s">
-        <v>681</v>
+        <v>674</v>
       </c>
       <c r="C135" t="s">
-        <v>736</v>
+        <v>725</v>
       </c>
       <c r="D135" t="s">
         <v>23</v>
@@ -7039,30 +7696,30 @@
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A136" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B136" t="s">
-        <v>684</v>
+        <v>677</v>
       </c>
       <c r="C136" t="s">
-        <v>736</v>
+        <v>725</v>
       </c>
       <c r="D136" t="s">
         <v>21</v>
       </c>
       <c r="E136" t="s">
-        <v>685</v>
+        <v>678</v>
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A137" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B137" t="s">
-        <v>682</v>
+        <v>675</v>
       </c>
       <c r="C137" t="s">
-        <v>736</v>
+        <v>725</v>
       </c>
       <c r="D137" t="s">
         <v>21</v>
@@ -7070,13 +7727,13 @@
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A138" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B138" t="s">
-        <v>683</v>
+        <v>676</v>
       </c>
       <c r="C138" t="s">
-        <v>736</v>
+        <v>725</v>
       </c>
       <c r="D138" t="s">
         <v>21</v>
@@ -7084,13 +7741,13 @@
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A139" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B139" t="s">
-        <v>687</v>
+        <v>680</v>
       </c>
       <c r="C139" t="s">
-        <v>737</v>
+        <v>726</v>
       </c>
       <c r="D139" t="s">
         <v>23</v>
@@ -7098,13 +7755,13 @@
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A140" s="2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B140" t="s">
-        <v>688</v>
+        <v>681</v>
       </c>
       <c r="C140" t="s">
-        <v>737</v>
+        <v>726</v>
       </c>
       <c r="D140" t="s">
         <v>23</v>
@@ -7112,13 +7769,13 @@
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A141" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B141" t="s">
-        <v>689</v>
+        <v>682</v>
       </c>
       <c r="C141" t="s">
-        <v>737</v>
+        <v>726</v>
       </c>
       <c r="D141" t="s">
         <v>23</v>
@@ -7126,13 +7783,13 @@
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A142" s="2" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B142" t="s">
-        <v>690</v>
+        <v>683</v>
       </c>
       <c r="C142" t="s">
-        <v>737</v>
+        <v>726</v>
       </c>
       <c r="D142" t="s">
         <v>23</v>
@@ -7140,1765 +7797,1867 @@
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A143" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B143" t="s">
-        <v>691</v>
+        <v>684</v>
       </c>
       <c r="C143" t="s">
-        <v>738</v>
+        <v>727</v>
       </c>
       <c r="D143" t="s">
         <v>23</v>
+      </c>
+      <c r="E143" t="s">
+        <v>906</v>
       </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A144" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B144" t="s">
-        <v>692</v>
+        <v>685</v>
       </c>
       <c r="C144" t="s">
-        <v>738</v>
+        <v>727</v>
       </c>
       <c r="D144" t="s">
         <v>21</v>
       </c>
+      <c r="E144" t="s">
+        <v>907</v>
+      </c>
     </row>
     <row r="145" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A145" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B145" t="s">
-        <v>693</v>
+        <v>686</v>
       </c>
       <c r="C145" t="s">
-        <v>738</v>
+        <v>727</v>
       </c>
       <c r="D145" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="146" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="E145" t="s">
+        <v>907</v>
+      </c>
+    </row>
+    <row r="146" spans="1:10" ht="28" x14ac:dyDescent="0.3">
       <c r="A146" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B146" t="s">
-        <v>694</v>
+        <v>687</v>
       </c>
       <c r="C146" t="s">
-        <v>739</v>
+        <v>728</v>
       </c>
       <c r="D146" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="147" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="E146" t="s">
+        <v>904</v>
+      </c>
+      <c r="F146">
+        <v>21</v>
+      </c>
+      <c r="G146">
+        <v>166</v>
+      </c>
+      <c r="H146" t="s">
+        <v>914</v>
+      </c>
+      <c r="J146" s="1" t="s">
+        <v>908</v>
+      </c>
+    </row>
+    <row r="147" spans="1:10" ht="42" x14ac:dyDescent="0.3">
       <c r="A147" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B147" t="s">
-        <v>695</v>
+        <v>688</v>
       </c>
       <c r="C147" t="s">
-        <v>739</v>
+        <v>728</v>
       </c>
       <c r="D147" t="s">
         <v>23</v>
+      </c>
+      <c r="E147" t="s">
+        <v>903</v>
+      </c>
+      <c r="F147">
+        <v>25</v>
+      </c>
+      <c r="G147">
+        <v>178</v>
+      </c>
+      <c r="H147" t="s">
+        <v>914</v>
+      </c>
+      <c r="J147" s="1" t="s">
+        <v>917</v>
       </c>
     </row>
     <row r="148" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A148" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="B148" t="s">
+        <v>692</v>
+      </c>
+      <c r="C148" t="s">
+        <v>728</v>
+      </c>
+      <c r="D148" t="s">
+        <v>23</v>
+      </c>
+      <c r="E148" t="s">
+        <v>905</v>
+      </c>
+      <c r="F148">
+        <v>60</v>
+      </c>
+      <c r="G148">
+        <v>172</v>
+      </c>
+      <c r="H148" t="s">
+        <v>914</v>
+      </c>
+      <c r="J148" t="s">
+        <v>909</v>
+      </c>
+    </row>
+    <row r="149" spans="1:10" ht="28" x14ac:dyDescent="0.3">
+      <c r="A149" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="B148" t="s">
-        <v>699</v>
-      </c>
-      <c r="C148" t="s">
-        <v>739</v>
-      </c>
-      <c r="D148" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="149" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A149" s="2" t="s">
-        <v>221</v>
-      </c>
       <c r="B149" t="s">
-        <v>696</v>
+        <v>689</v>
       </c>
       <c r="C149" t="s">
-        <v>739</v>
+        <v>728</v>
       </c>
       <c r="D149" t="s">
         <v>21</v>
       </c>
+      <c r="E149" t="s">
+        <v>912</v>
+      </c>
+      <c r="F149">
+        <v>45</v>
+      </c>
+      <c r="G149">
+        <v>165</v>
+      </c>
+      <c r="H149" t="s">
+        <v>914</v>
+      </c>
+      <c r="J149" s="1" t="s">
+        <v>911</v>
+      </c>
     </row>
     <row r="150" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A150" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B150" t="s">
-        <v>697</v>
+        <v>690</v>
       </c>
       <c r="C150" t="s">
-        <v>739</v>
+        <v>728</v>
       </c>
       <c r="D150" t="s">
         <v>23</v>
+      </c>
+      <c r="E150" t="s">
+        <v>913</v>
+      </c>
+      <c r="F150">
+        <v>36</v>
+      </c>
+      <c r="G150">
+        <v>181</v>
+      </c>
+      <c r="H150" t="s">
+        <v>914</v>
+      </c>
+      <c r="J150" t="s">
+        <v>910</v>
       </c>
     </row>
     <row r="151" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A151" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B151" t="s">
-        <v>698</v>
+        <v>691</v>
       </c>
       <c r="C151" t="s">
-        <v>740</v>
+        <v>729</v>
       </c>
       <c r="D151" t="s">
         <v>23</v>
+      </c>
+      <c r="E151" t="s">
+        <v>915</v>
+      </c>
+      <c r="F151" t="s">
+        <v>540</v>
+      </c>
+      <c r="G151">
+        <v>198</v>
+      </c>
+      <c r="H151" t="s">
+        <v>540</v>
+      </c>
+      <c r="J151" s="1" t="s">
+        <v>916</v>
       </c>
     </row>
     <row r="152" spans="1:10" ht="56" x14ac:dyDescent="0.3">
       <c r="A152" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B152" t="s">
-        <v>700</v>
+        <v>693</v>
       </c>
       <c r="C152" t="s">
-        <v>742</v>
+        <v>731</v>
       </c>
       <c r="D152" t="s">
         <v>23</v>
       </c>
       <c r="E152" t="s">
-        <v>846</v>
+        <v>830</v>
       </c>
       <c r="G152">
         <v>180</v>
       </c>
       <c r="H152" t="s">
-        <v>848</v>
+        <v>832</v>
       </c>
       <c r="J152" s="1" t="s">
-        <v>847</v>
+        <v>831</v>
       </c>
     </row>
     <row r="153" spans="1:10" ht="28" x14ac:dyDescent="0.3">
       <c r="A153" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B153" t="s">
-        <v>701</v>
+        <v>694</v>
       </c>
       <c r="C153" t="s">
-        <v>742</v>
+        <v>731</v>
       </c>
       <c r="D153" t="s">
         <v>21</v>
       </c>
       <c r="E153" t="s">
-        <v>828</v>
+        <v>814</v>
       </c>
       <c r="G153">
         <v>164</v>
       </c>
       <c r="H153" t="s">
-        <v>848</v>
+        <v>832</v>
       </c>
       <c r="J153" s="1" t="s">
-        <v>829</v>
+        <v>815</v>
       </c>
     </row>
     <row r="154" spans="1:10" ht="70" x14ac:dyDescent="0.3">
       <c r="A154" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B154" t="s">
-        <v>825</v>
+        <v>811</v>
       </c>
       <c r="C154" t="s">
-        <v>742</v>
+        <v>731</v>
       </c>
       <c r="D154" t="s">
         <v>23</v>
       </c>
       <c r="E154" t="s">
-        <v>826</v>
+        <v>812</v>
       </c>
       <c r="G154">
         <v>176</v>
       </c>
       <c r="H154" t="s">
-        <v>850</v>
+        <v>834</v>
       </c>
       <c r="J154" s="1" t="s">
-        <v>832</v>
+        <v>818</v>
       </c>
     </row>
     <row r="155" spans="1:10" ht="56" x14ac:dyDescent="0.3">
       <c r="A155" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B155" t="s">
-        <v>824</v>
+        <v>810</v>
       </c>
       <c r="C155" t="s">
-        <v>742</v>
+        <v>731</v>
       </c>
       <c r="D155" t="s">
         <v>23</v>
       </c>
       <c r="E155" t="s">
-        <v>827</v>
+        <v>813</v>
       </c>
       <c r="G155">
         <v>185</v>
       </c>
       <c r="H155" t="s">
-        <v>848</v>
+        <v>832</v>
       </c>
       <c r="J155" s="1" t="s">
-        <v>845</v>
+        <v>829</v>
       </c>
     </row>
     <row r="156" spans="1:10" ht="84" x14ac:dyDescent="0.3">
       <c r="A156" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B156" t="s">
-        <v>702</v>
+        <v>695</v>
       </c>
       <c r="C156" t="s">
-        <v>743</v>
+        <v>732</v>
       </c>
       <c r="D156" t="s">
         <v>21</v>
       </c>
       <c r="E156" t="s">
-        <v>852</v>
+        <v>836</v>
       </c>
       <c r="G156">
         <v>166</v>
       </c>
       <c r="H156" t="s">
-        <v>743</v>
+        <v>732</v>
       </c>
       <c r="J156" s="1" t="s">
-        <v>844</v>
+        <v>828</v>
       </c>
     </row>
     <row r="157" spans="1:10" ht="28" x14ac:dyDescent="0.3">
       <c r="A157" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B157" t="s">
-        <v>703</v>
+        <v>696</v>
       </c>
       <c r="C157" t="s">
-        <v>743</v>
+        <v>732</v>
       </c>
       <c r="D157" t="s">
         <v>21</v>
       </c>
       <c r="E157" t="s">
-        <v>851</v>
+        <v>835</v>
       </c>
       <c r="G157">
         <v>166</v>
       </c>
       <c r="H157" t="s">
-        <v>743</v>
+        <v>732</v>
       </c>
       <c r="J157" s="1" t="s">
-        <v>823</v>
+        <v>809</v>
       </c>
     </row>
     <row r="158" spans="1:10" ht="42" x14ac:dyDescent="0.3">
       <c r="A158" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B158" t="s">
-        <v>705</v>
+        <v>698</v>
       </c>
       <c r="C158" t="s">
-        <v>743</v>
+        <v>732</v>
       </c>
       <c r="D158" t="s">
         <v>23</v>
       </c>
       <c r="E158" t="s">
-        <v>853</v>
+        <v>837</v>
       </c>
       <c r="G158">
         <v>182</v>
       </c>
       <c r="H158" t="s">
-        <v>849</v>
+        <v>833</v>
       </c>
       <c r="J158" s="1" t="s">
-        <v>831</v>
+        <v>817</v>
       </c>
     </row>
     <row r="159" spans="1:10" ht="28" x14ac:dyDescent="0.3">
       <c r="A159" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B159" t="s">
-        <v>704</v>
+        <v>697</v>
       </c>
       <c r="C159" t="s">
-        <v>757</v>
+        <v>746</v>
       </c>
       <c r="D159" t="s">
         <v>23</v>
       </c>
       <c r="E159" t="s">
-        <v>855</v>
+        <v>839</v>
       </c>
       <c r="G159">
         <v>178</v>
       </c>
       <c r="H159" t="s">
-        <v>849</v>
+        <v>833</v>
       </c>
       <c r="J159" s="1" t="s">
-        <v>830</v>
+        <v>816</v>
       </c>
     </row>
     <row r="160" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A160" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B160" t="s">
-        <v>741</v>
+        <v>730</v>
       </c>
       <c r="C160" t="s">
-        <v>757</v>
+        <v>746</v>
       </c>
       <c r="D160" t="s">
         <v>23</v>
       </c>
       <c r="E160" t="s">
-        <v>854</v>
+        <v>838</v>
       </c>
       <c r="G160">
         <v>173</v>
       </c>
       <c r="H160" t="s">
-        <v>849</v>
+        <v>833</v>
       </c>
     </row>
     <row r="161" spans="1:10" ht="70" x14ac:dyDescent="0.3">
       <c r="A161" s="2" t="s">
-        <v>758</v>
+        <v>747</v>
       </c>
       <c r="B161" t="s">
-        <v>759</v>
+        <v>748</v>
       </c>
       <c r="C161" t="s">
-        <v>730</v>
+        <v>719</v>
       </c>
       <c r="D161" t="s">
         <v>21</v>
       </c>
       <c r="E161" t="s">
-        <v>788</v>
+        <v>776</v>
       </c>
       <c r="F161">
         <v>21</v>
       </c>
       <c r="G161" t="s">
-        <v>790</v>
+        <v>778</v>
       </c>
       <c r="H161" t="s">
         <v>30</v>
       </c>
       <c r="J161" s="1" t="s">
-        <v>791</v>
+        <v>779</v>
       </c>
     </row>
     <row r="162" spans="1:10" ht="28" x14ac:dyDescent="0.3">
       <c r="A162" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B162" t="s">
-        <v>761</v>
+        <v>750</v>
       </c>
       <c r="C162" t="s">
-        <v>734</v>
+        <v>723</v>
       </c>
       <c r="D162" t="s">
         <v>21</v>
       </c>
+      <c r="E162" t="s">
+        <v>869</v>
+      </c>
       <c r="J162" s="1" t="s">
-        <v>843</v>
+        <v>827</v>
       </c>
     </row>
     <row r="163" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A163" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="164" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A164" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="165" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A165" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="166" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A166" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="167" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A167" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="168" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A168" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="169" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A169" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="170" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A170" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="171" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A171" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="172" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A172" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="173" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A173" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="174" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A174" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="175" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A175" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="176" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A176" s="2" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="177" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A177" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="178" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A178" s="2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="179" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A179" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="180" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A180" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="181" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A181" s="2" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="182" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A182" s="2" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="183" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A183" s="2" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="184" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A184" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="185" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A185" s="2" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="186" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A186" s="2" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="187" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A187" s="2" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="188" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A188" s="2" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="189" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A189" s="2" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="190" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A190" s="2" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="191" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A191" s="2" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="192" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A192" s="2" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="193" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A193" s="2" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="194" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A194" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="195" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A195" s="2" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="196" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A196" s="2" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="197" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A197" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="198" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A198" s="2" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="199" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A199" s="2" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="200" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A200" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="201" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A201" s="2" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="202" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A202" s="2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="203" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A203" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="204" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A204" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="205" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A205" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="206" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A206" s="2" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="207" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A207" s="2" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="208" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A208" s="2" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="209" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A209" s="2" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="210" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A210" s="2" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="211" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A211" s="2" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="212" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A212" s="2" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="213" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A213" s="2" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="214" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A214" s="2" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="215" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A215" s="2" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="216" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A216" s="2" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="217" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A217" s="2" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="218" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A218" s="2" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="219" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A219" s="2" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="220" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A220" s="2" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="221" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A221" s="2" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="222" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A222" s="2" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="223" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A223" s="2" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="224" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A224" s="2" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="225" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A225" s="2" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="226" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A226" s="2" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="227" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A227" s="2" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="228" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A228" s="2" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="229" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A229" s="2" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="230" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A230" s="2" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="231" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A231" s="2" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="232" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A232" s="2" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="233" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A233" s="2" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="234" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A234" s="2" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="235" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A235" s="2" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="236" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A236" s="2" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="237" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A237" s="2" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="238" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A238" s="2" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="239" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A239" s="2" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="240" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A240" s="2" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="241" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A241" s="2" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="242" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A242" s="2" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="243" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A243" s="2" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="244" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A244" s="2" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="245" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A245" s="2" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="246" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A246" s="2" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="247" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A247" s="2" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="248" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A248" s="2" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="249" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A249" s="2" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="250" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A250" s="2" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="251" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A251" s="2" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="252" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A252" s="2" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="253" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A253" s="2" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="254" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A254" s="2" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="255" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A255" s="2" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="256" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A256" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="257" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A257" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="258" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A258" s="2" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="259" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A259" s="2" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="260" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A260" s="2" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="261" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A261" s="2" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="262" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A262" s="2" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="263" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A263" s="2" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="264" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A264" s="2" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="265" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A265" s="2" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="266" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A266" s="2" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="267" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A267" s="2" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="268" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A268" s="2" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="269" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A269" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="270" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A270" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="271" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A271" s="2" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="272" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A272" s="2" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="273" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A273" s="2" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="274" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A274" s="2" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="275" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A275" s="2" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="276" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A276" s="2" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="277" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A277" s="2" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="278" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A278" s="2" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="279" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A279" s="2" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="280" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A280" s="2" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="281" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A281" s="2" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="282" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A282" s="2" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="283" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A283" s="2" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="284" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A284" s="2" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="285" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A285" s="2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="286" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A286" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="287" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A287" s="2" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="288" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A288" s="2" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="289" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A289" s="2" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="290" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A290" s="2" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="291" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A291" s="2" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="292" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A292" s="2" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="293" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A293" s="2" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="294" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A294" s="2" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="295" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A295" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="296" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A296" s="2" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="297" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A297" s="2" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="298" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A298" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="299" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A299" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="300" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A300" s="2" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="301" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A301" s="2" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="302" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A302" s="2" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="303" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A303" s="2" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="304" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A304" s="2" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="305" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A305" s="2" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="306" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A306" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="307" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A307" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="308" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A308" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="309" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A309" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="310" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A310" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="311" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A311" s="2" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="312" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A312" s="2" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="313" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A313" s="2" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="314" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A314" s="2" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="315" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A315" s="2" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="316" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A316" s="2" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="317" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A317" s="2" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="318" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A318" s="2" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="319" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A319" s="2" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="320" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A320" s="2" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="321" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A321" s="2" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="322" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A322" s="2" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="323" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A323" s="2" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="324" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A324" s="2" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="325" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A325" s="2" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="326" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A326" s="2" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="327" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A327" s="2" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="328" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A328" s="2" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="329" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A329" s="2" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="330" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A330" s="2" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="331" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A331" s="2" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="332" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A332" s="2" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="333" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A333" s="2" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="334" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A334" s="2" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="335" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A335" s="2" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="336" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A336" s="2" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="337" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A337" s="2" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="338" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A338" s="2" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="339" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A339" s="2" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="340" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A340" s="2" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="341" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A341" s="2" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="342" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A342" s="2" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="343" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A343" s="2" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="344" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A344" s="2" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="345" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A345" s="2" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="346" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A346" s="2" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="347" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A347" s="2" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="348" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A348" s="2" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="349" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A349" s="2" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="350" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A350" s="2" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="351" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A351" s="2" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="352" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A352" s="2" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="353" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A353" s="2" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="354" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A354" s="2" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="355" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A355" s="2" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="356" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A356" s="2" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="357" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A357" s="2" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="358" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A358" s="2" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="359" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A359" s="2" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="360" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A360" s="2" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="361" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A361" s="2" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="362" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A362" s="2" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="363" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A363" s="2" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="364" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A364" s="2" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="365" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A365" s="2" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="366" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A366" s="2" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="367" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A367" s="2" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="368" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A368" s="2" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="369" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A369" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="370" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A370" s="2" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="371" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A371" s="2" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="372" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A372" s="2" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="373" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A373" s="2" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="374" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A374" s="2" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="375" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A375" s="2" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="376" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A376" s="2" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="377" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A377" s="2" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="378" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A378" s="2" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="379" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A379" s="2" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="380" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A380" s="2" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="381" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A381" s="2" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="382" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A382" s="2" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="383" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A383" s="2" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="384" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A384" s="2" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="385" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A385" s="2" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="386" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A386" s="2" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="387" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A387" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="388" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A388" s="2" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="389" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A389" s="2" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="390" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A390" s="2" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="391" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A391" s="2" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="392" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A392" s="2" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="393" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A393" s="2" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="394" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A394" s="2" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="395" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A395" s="2" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="396" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A396" s="2" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="397" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A397" s="2" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="398" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A398" s="2" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="399" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A399" s="2" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="400" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A400" s="2" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="401" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A401" s="2" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="402" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A402" s="2" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="403" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A403" s="2" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="404" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A404" s="2" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="405" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A405" s="2" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="406" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A406" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="407" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A407" s="2" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="408" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A408" s="2" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="409" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A409" s="2" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
     </row>
     <row r="410" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A410" s="2" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="411" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A411" s="2" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="412" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A412" s="2" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="413" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A413" s="2" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="414" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A414" s="2" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="415" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A415" s="2" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="416" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A416" s="2" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="417" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A417" s="2" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="418" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A418" s="2" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="419" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A419" s="2" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="420" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A420" s="2" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="421" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A421" s="2" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="422" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A422" s="2" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="423" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A423" s="2" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="424" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A424" s="2" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="425" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A425" s="2" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="426" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A426" s="2" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="427" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A427" s="2" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
     <row r="428" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A428" s="2" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="429" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A429" s="2" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="430" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A430" s="2" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="431" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A431" s="2" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="432" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A432" s="2" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="433" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A433" s="2" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="434" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A434" s="2" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
   </sheetData>

--- a/人物合集.xlsx
+++ b/人物合集.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\xiaoshuo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED422C10-28DA-460C-9AFB-48DB28877E6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{046D41C0-6E73-4D20-9D39-BF14327C1CC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21820" xr2:uid="{AF08DE20-9936-418E-B994-1A830DDDD9DE}"/>
+    <workbookView xWindow="2240" yWindow="2240" windowWidth="28800" windowHeight="15910" xr2:uid="{AF08DE20-9936-418E-B994-1A830DDDD9DE}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1414" uniqueCount="918">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1442" uniqueCount="936">
   <si>
     <t>name</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -3473,10 +3473,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>热情似火的大漠姑娘。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>拜火教老城主。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -3498,24 +3494,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>胡四娘：依靠</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>铃兰：结义姐妹
-阿贺：照顾</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>彝城包子铺的老板娘，似乎与大漠拜火教有瓜葛。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>芦城边缘的算账人。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>大漠</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -3530,6 +3513,107 @@
     <t>图娜：未婚妻
 老城主：父亲
 法鲁克：好友</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>阿塔什</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>黑铁</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>终年52</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>终年40</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>月泉城</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>芦城</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>彝城</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>拜火教大护法，与胡四娘、黑铁、铃兰结义的大哥。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>拜火教元老，阿贺的兄长。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>铃兰：妻子
+图娜：女儿
+老城主：下属
+胡四娘：义妹
+黑铁：义弟</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>黑铁：兄长
+胡四娘：依靠</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>阿塔什：义兄
+黑铁：义兄
+铃兰：义姊
+阿贺：照顾</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>阿塔什：义兄
+铃兰：义妹
+胡四娘：义妹
+阿贺：弟弟</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>拜火教大护法之女，向往自由、热情似火的大漠姑娘。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>狐仙姐姐：信赖</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>赤狐：自己
+翠娥：照顾
+芸茴：照顾</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>风鹰：自己</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>潜风谷谷主，为人谦逊温和，喜欢自称“小生”。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>本名余庆怀，祁云亲王次子。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>猫爷儿子。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>绰号“灰猫”，潜风谷救济的大漠难民。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>卿衍：恩人</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -7596,7 +7680,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A129" s="2" t="s">
         <v>200</v>
       </c>
@@ -7610,7 +7694,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A130" s="2" t="s">
         <v>201</v>
       </c>
@@ -7624,7 +7708,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A131" s="2" t="s">
         <v>202</v>
       </c>
@@ -7638,7 +7722,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A132" s="2" t="s">
         <v>203</v>
       </c>
@@ -7652,7 +7736,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A133" s="2" t="s">
         <v>204</v>
       </c>
@@ -7666,7 +7750,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A134" s="2" t="s">
         <v>205</v>
       </c>
@@ -7680,7 +7764,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A135" s="2" t="s">
         <v>206</v>
       </c>
@@ -7694,7 +7778,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A136" s="2" t="s">
         <v>207</v>
       </c>
@@ -7711,7 +7795,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A137" s="2" t="s">
         <v>208</v>
       </c>
@@ -7725,7 +7809,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A138" s="2" t="s">
         <v>209</v>
       </c>
@@ -7739,7 +7823,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A139" s="2" t="s">
         <v>210</v>
       </c>
@@ -7752,8 +7836,14 @@
       <c r="D139" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E139" t="s">
+        <v>931</v>
+      </c>
+      <c r="J139" t="s">
+        <v>930</v>
+      </c>
+    </row>
+    <row r="140" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A140" s="2" t="s">
         <v>211</v>
       </c>
@@ -7766,8 +7856,17 @@
       <c r="D140" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E140" t="s">
+        <v>932</v>
+      </c>
+      <c r="H140" t="s">
+        <v>39</v>
+      </c>
+      <c r="J140" t="s">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="141" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A141" s="2" t="s">
         <v>212</v>
       </c>
@@ -7780,8 +7879,14 @@
       <c r="D141" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E141" t="s">
+        <v>934</v>
+      </c>
+      <c r="J141" t="s">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="142" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A142" s="2" t="s">
         <v>213</v>
       </c>
@@ -7794,8 +7899,11 @@
       <c r="D142" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E142" t="s">
+        <v>933</v>
+      </c>
+    </row>
+    <row r="143" spans="1:10" ht="42" x14ac:dyDescent="0.3">
       <c r="A143" s="2" t="s">
         <v>214</v>
       </c>
@@ -7809,10 +7917,13 @@
         <v>23</v>
       </c>
       <c r="E143" t="s">
-        <v>906</v>
-      </c>
-    </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.3">
+        <v>905</v>
+      </c>
+      <c r="J143" s="1" t="s">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="144" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A144" s="2" t="s">
         <v>215</v>
       </c>
@@ -7826,7 +7937,10 @@
         <v>21</v>
       </c>
       <c r="E144" t="s">
-        <v>907</v>
+        <v>906</v>
+      </c>
+      <c r="J144" t="s">
+        <v>928</v>
       </c>
     </row>
     <row r="145" spans="1:10" x14ac:dyDescent="0.3">
@@ -7843,7 +7957,10 @@
         <v>21</v>
       </c>
       <c r="E145" t="s">
-        <v>907</v>
+        <v>906</v>
+      </c>
+      <c r="J145" t="s">
+        <v>928</v>
       </c>
     </row>
     <row r="146" spans="1:10" ht="28" x14ac:dyDescent="0.3">
@@ -7860,7 +7977,7 @@
         <v>21</v>
       </c>
       <c r="E146" t="s">
-        <v>904</v>
+        <v>927</v>
       </c>
       <c r="F146">
         <v>21</v>
@@ -7869,10 +7986,10 @@
         <v>166</v>
       </c>
       <c r="H146" t="s">
-        <v>914</v>
+        <v>918</v>
       </c>
       <c r="J146" s="1" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
     </row>
     <row r="147" spans="1:10" ht="42" x14ac:dyDescent="0.3">
@@ -7898,10 +8015,10 @@
         <v>178</v>
       </c>
       <c r="H147" t="s">
-        <v>914</v>
+        <v>918</v>
       </c>
       <c r="J147" s="1" t="s">
-        <v>917</v>
+        <v>913</v>
       </c>
     </row>
     <row r="148" spans="1:10" x14ac:dyDescent="0.3">
@@ -7918,7 +8035,7 @@
         <v>23</v>
       </c>
       <c r="E148" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="F148">
         <v>60</v>
@@ -7927,13 +8044,13 @@
         <v>172</v>
       </c>
       <c r="H148" t="s">
-        <v>914</v>
+        <v>918</v>
       </c>
       <c r="J148" t="s">
-        <v>909</v>
-      </c>
-    </row>
-    <row r="149" spans="1:10" ht="28" x14ac:dyDescent="0.3">
+        <v>908</v>
+      </c>
+    </row>
+    <row r="149" spans="1:10" ht="56" x14ac:dyDescent="0.3">
       <c r="A149" s="2" t="s">
         <v>220</v>
       </c>
@@ -7947,7 +8064,7 @@
         <v>21</v>
       </c>
       <c r="E149" t="s">
-        <v>912</v>
+        <v>909</v>
       </c>
       <c r="F149">
         <v>45</v>
@@ -7956,13 +8073,13 @@
         <v>165</v>
       </c>
       <c r="H149" t="s">
-        <v>914</v>
+        <v>920</v>
       </c>
       <c r="J149" s="1" t="s">
-        <v>911</v>
-      </c>
-    </row>
-    <row r="150" spans="1:10" x14ac:dyDescent="0.3">
+        <v>925</v>
+      </c>
+    </row>
+    <row r="150" spans="1:10" ht="28" x14ac:dyDescent="0.3">
       <c r="A150" s="2" t="s">
         <v>221</v>
       </c>
@@ -7976,7 +8093,7 @@
         <v>23</v>
       </c>
       <c r="E150" t="s">
-        <v>913</v>
+        <v>910</v>
       </c>
       <c r="F150">
         <v>36</v>
@@ -7985,10 +8102,10 @@
         <v>181</v>
       </c>
       <c r="H150" t="s">
-        <v>914</v>
-      </c>
-      <c r="J150" t="s">
-        <v>910</v>
+        <v>919</v>
+      </c>
+      <c r="J150" s="1" t="s">
+        <v>924</v>
       </c>
     </row>
     <row r="151" spans="1:10" x14ac:dyDescent="0.3">
@@ -8005,7 +8122,7 @@
         <v>23</v>
       </c>
       <c r="E151" t="s">
-        <v>915</v>
+        <v>911</v>
       </c>
       <c r="F151" t="s">
         <v>540</v>
@@ -8017,7 +8134,7 @@
         <v>540</v>
       </c>
       <c r="J151" s="1" t="s">
-        <v>916</v>
+        <v>912</v>
       </c>
     </row>
     <row r="152" spans="1:10" ht="56" x14ac:dyDescent="0.3">
@@ -8296,18 +8413,75 @@
       <c r="E162" t="s">
         <v>869</v>
       </c>
+      <c r="F162" t="s">
+        <v>540</v>
+      </c>
+      <c r="G162" t="s">
+        <v>540</v>
+      </c>
+      <c r="H162" t="s">
+        <v>540</v>
+      </c>
       <c r="J162" s="1" t="s">
         <v>827</v>
       </c>
     </row>
-    <row r="163" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:10" ht="70" x14ac:dyDescent="0.3">
       <c r="A163" s="2" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="164" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B163" t="s">
+        <v>914</v>
+      </c>
+      <c r="C163" t="s">
+        <v>728</v>
+      </c>
+      <c r="D163" t="s">
+        <v>23</v>
+      </c>
+      <c r="E163" t="s">
+        <v>921</v>
+      </c>
+      <c r="F163" t="s">
+        <v>916</v>
+      </c>
+      <c r="G163">
+        <v>190</v>
+      </c>
+      <c r="H163" t="s">
+        <v>918</v>
+      </c>
+      <c r="J163" s="1" t="s">
+        <v>923</v>
+      </c>
+    </row>
+    <row r="164" spans="1:10" ht="56" x14ac:dyDescent="0.3">
       <c r="A164" s="2" t="s">
         <v>234</v>
+      </c>
+      <c r="B164" t="s">
+        <v>915</v>
+      </c>
+      <c r="C164" t="s">
+        <v>728</v>
+      </c>
+      <c r="D164" t="s">
+        <v>23</v>
+      </c>
+      <c r="E164" t="s">
+        <v>922</v>
+      </c>
+      <c r="F164" t="s">
+        <v>917</v>
+      </c>
+      <c r="G164">
+        <v>174</v>
+      </c>
+      <c r="H164" t="s">
+        <v>919</v>
+      </c>
+      <c r="J164" s="1" t="s">
+        <v>926</v>
       </c>
     </row>
     <row r="165" spans="1:10" x14ac:dyDescent="0.3">

--- a/人物合集.xlsx
+++ b/人物合集.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\xiaoshuo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{046D41C0-6E73-4D20-9D39-BF14327C1CC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68A91E9B-3DE9-4B77-9793-803B3DD78AD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2240" yWindow="2240" windowWidth="28800" windowHeight="15910" xr2:uid="{AF08DE20-9936-418E-B994-1A830DDDD9DE}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1442" uniqueCount="936">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1479" uniqueCount="952">
   <si>
     <t>name</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -3614,6 +3614,84 @@
   </si>
   <si>
     <t>卿衍：恩人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>当朝帝王。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>佑帝同父异母之妹，长公主。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>翟琳儿，佑帝太子时期执意接进东宫的风尘女子。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>翟皇后：妻子
+衍丰太子：儿子
+清乡公主：妹妹
+知微国师：臣子
+向秀：臣子
+向珣：臣子</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>灾凤：自己
+佑帝：夫君
+衍丰太子：儿子</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>当朝太子。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>当朝国师。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>太子仙师。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>佑帝：哥哥</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>佑帝：父亲
+翟皇后：母亲
+漆九：老师</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>佑帝：国君
+漆九：弟子</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>知微国师：老师
+衍丰太子：徒弟</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>当朝大将军，被封为镇国侯。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>镇国侯次子，名满皇都的向小侯爷。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>佑帝：国君
+向鼎：长子
+向珣：次子</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>佑帝：国君
+向秀：父亲</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -6080,6 +6158,9 @@
       <c r="E62" t="s">
         <v>771</v>
       </c>
+      <c r="F62" t="s">
+        <v>540</v>
+      </c>
       <c r="G62">
         <v>175</v>
       </c>
@@ -6106,6 +6187,12 @@
       <c r="E63" t="s">
         <v>896</v>
       </c>
+      <c r="F63">
+        <v>66</v>
+      </c>
+      <c r="H63" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="64" spans="1:11" ht="42" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
@@ -6123,8 +6210,14 @@
       <c r="E64" t="s">
         <v>897</v>
       </c>
+      <c r="F64" t="s">
+        <v>540</v>
+      </c>
       <c r="G64">
         <v>178</v>
+      </c>
+      <c r="H64" t="s">
+        <v>34</v>
       </c>
       <c r="J64" s="1" t="s">
         <v>902</v>
@@ -6146,6 +6239,12 @@
       <c r="E65" t="s">
         <v>898</v>
       </c>
+      <c r="F65">
+        <v>48</v>
+      </c>
+      <c r="H65" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
@@ -6163,6 +6262,12 @@
       <c r="E66" t="s">
         <v>898</v>
       </c>
+      <c r="F66">
+        <v>58</v>
+      </c>
+      <c r="H66" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
@@ -6180,6 +6285,12 @@
       <c r="E67" t="s">
         <v>898</v>
       </c>
+      <c r="F67">
+        <v>43</v>
+      </c>
+      <c r="H67" t="s">
+        <v>707</v>
+      </c>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
@@ -6197,6 +6308,12 @@
       <c r="E68" t="s">
         <v>898</v>
       </c>
+      <c r="F68">
+        <v>38</v>
+      </c>
+      <c r="H68" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="69" spans="1:10" ht="28" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
@@ -6214,6 +6331,15 @@
       <c r="E69" t="s">
         <v>899</v>
       </c>
+      <c r="F69">
+        <v>24</v>
+      </c>
+      <c r="G69">
+        <v>160</v>
+      </c>
+      <c r="H69" t="s">
+        <v>31</v>
+      </c>
       <c r="J69" s="1" t="s">
         <v>900</v>
       </c>
@@ -6234,6 +6360,15 @@
       <c r="E70" t="s">
         <v>899</v>
       </c>
+      <c r="F70">
+        <v>18</v>
+      </c>
+      <c r="G70">
+        <v>175</v>
+      </c>
+      <c r="H70" t="s">
+        <v>31</v>
+      </c>
       <c r="J70" t="s">
         <v>901</v>
       </c>
@@ -6254,6 +6389,15 @@
       <c r="E71" t="s">
         <v>899</v>
       </c>
+      <c r="F71">
+        <v>17</v>
+      </c>
+      <c r="G71">
+        <v>179</v>
+      </c>
+      <c r="H71" t="s">
+        <v>31</v>
+      </c>
       <c r="J71" t="s">
         <v>901</v>
       </c>
@@ -6274,6 +6418,15 @@
       <c r="E72" t="s">
         <v>899</v>
       </c>
+      <c r="F72">
+        <v>28</v>
+      </c>
+      <c r="G72">
+        <v>173</v>
+      </c>
+      <c r="H72" t="s">
+        <v>707</v>
+      </c>
       <c r="J72" t="s">
         <v>881</v>
       </c>
@@ -7568,7 +7721,7 @@
         <v>864</v>
       </c>
     </row>
-    <row r="121" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:10" ht="84" x14ac:dyDescent="0.3">
       <c r="A121" s="2" t="s">
         <v>192</v>
       </c>
@@ -7581,8 +7734,23 @@
       <c r="D121" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="122" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="E121" t="s">
+        <v>936</v>
+      </c>
+      <c r="F121">
+        <v>55</v>
+      </c>
+      <c r="G121">
+        <v>178</v>
+      </c>
+      <c r="H121" t="s">
+        <v>31</v>
+      </c>
+      <c r="J121" s="1" t="s">
+        <v>939</v>
+      </c>
+    </row>
+    <row r="122" spans="1:10" ht="42" x14ac:dyDescent="0.3">
       <c r="A122" s="2" t="s">
         <v>193</v>
       </c>
@@ -7594,6 +7762,21 @@
       </c>
       <c r="D122" t="s">
         <v>21</v>
+      </c>
+      <c r="E122" t="s">
+        <v>938</v>
+      </c>
+      <c r="F122" t="s">
+        <v>540</v>
+      </c>
+      <c r="G122">
+        <v>175</v>
+      </c>
+      <c r="H122" t="s">
+        <v>540</v>
+      </c>
+      <c r="J122" s="1" t="s">
+        <v>940</v>
       </c>
     </row>
     <row r="123" spans="1:10" x14ac:dyDescent="0.3">
@@ -7609,8 +7792,20 @@
       <c r="D123" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="124" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="E123" t="s">
+        <v>937</v>
+      </c>
+      <c r="F123">
+        <v>32</v>
+      </c>
+      <c r="H123" t="s">
+        <v>31</v>
+      </c>
+      <c r="J123" s="1" t="s">
+        <v>944</v>
+      </c>
+    </row>
+    <row r="124" spans="1:10" ht="42" x14ac:dyDescent="0.3">
       <c r="A124" s="2" t="s">
         <v>195</v>
       </c>
@@ -7623,8 +7818,20 @@
       <c r="D124" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="125" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="E124" t="s">
+        <v>941</v>
+      </c>
+      <c r="F124">
+        <v>28</v>
+      </c>
+      <c r="H124" t="s">
+        <v>31</v>
+      </c>
+      <c r="J124" s="1" t="s">
+        <v>945</v>
+      </c>
+    </row>
+    <row r="125" spans="1:10" ht="28" x14ac:dyDescent="0.3">
       <c r="A125" s="2" t="s">
         <v>196</v>
       </c>
@@ -7637,8 +7844,20 @@
       <c r="D125" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="126" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="E125" t="s">
+        <v>942</v>
+      </c>
+      <c r="F125">
+        <v>67</v>
+      </c>
+      <c r="H125" t="s">
+        <v>34</v>
+      </c>
+      <c r="J125" s="1" t="s">
+        <v>946</v>
+      </c>
+    </row>
+    <row r="126" spans="1:10" ht="28" x14ac:dyDescent="0.3">
       <c r="A126" s="2" t="s">
         <v>197</v>
       </c>
@@ -7651,8 +7870,20 @@
       <c r="D126" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="127" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="E126" t="s">
+        <v>943</v>
+      </c>
+      <c r="F126">
+        <v>25</v>
+      </c>
+      <c r="H126" t="s">
+        <v>707</v>
+      </c>
+      <c r="J126" s="1" t="s">
+        <v>947</v>
+      </c>
+    </row>
+    <row r="127" spans="1:10" ht="42" x14ac:dyDescent="0.3">
       <c r="A127" s="2" t="s">
         <v>198</v>
       </c>
@@ -7665,8 +7896,20 @@
       <c r="D127" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="128" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="E127" t="s">
+        <v>948</v>
+      </c>
+      <c r="F127">
+        <v>50</v>
+      </c>
+      <c r="H127" t="s">
+        <v>31</v>
+      </c>
+      <c r="J127" s="1" t="s">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="128" spans="1:10" ht="28" x14ac:dyDescent="0.3">
       <c r="A128" s="2" t="s">
         <v>199</v>
       </c>
@@ -7678,6 +7921,18 @@
       </c>
       <c r="D128" t="s">
         <v>23</v>
+      </c>
+      <c r="E128" t="s">
+        <v>949</v>
+      </c>
+      <c r="F128">
+        <v>17</v>
+      </c>
+      <c r="H128" t="s">
+        <v>31</v>
+      </c>
+      <c r="J128" s="1" t="s">
+        <v>951</v>
       </c>
     </row>
     <row r="129" spans="1:10" x14ac:dyDescent="0.3">
